--- a/PROJECTS_EXCEL/tests/PersonalEventBuilder/TestScenarios.xlsx
+++ b/PROJECTS_EXCEL/tests/PersonalEventBuilder/TestScenarios.xlsx
@@ -34724,739 +34724,755 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="59" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="59" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="59" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="59" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="59" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" s="59" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="59" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="T1" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="U1" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="V1" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="X1" s="59" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y1" s="59" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z1" s="59" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA1" s="59" t="s">
-        <v>31</v>
+      <c r="A1" s="59" t="str">
+        <v>ScenarioId</v>
+      </c>
+      <c r="B1" s="59" t="str">
+        <v>RowId</v>
+      </c>
+      <c r="C1" s="59" t="str">
+        <v>Звання</v>
+      </c>
+      <c r="D1" s="59" t="str">
+        <v>ПІБ</v>
+      </c>
+      <c r="E1" s="59" t="str">
+        <v>ІПН</v>
+      </c>
+      <c r="F1" s="59" t="str">
+        <v>Посада</v>
+      </c>
+      <c r="G1" s="59" t="str">
+        <v>Подія</v>
+      </c>
+      <c r="H1" s="60" t="str">
+        <v>Куди</v>
+      </c>
+      <c r="I1" s="59" t="str">
+        <v>За межі</v>
+      </c>
+      <c r="J1" s="59" t="str">
+        <v>Вибуття.Наказ</v>
+      </c>
+      <c r="K1" s="59" t="str">
+        <v>Вибуття.Продовольче</v>
+      </c>
+      <c r="L1" s="59" t="str">
+        <v>Вибуття</v>
+      </c>
+      <c r="M1" s="59" t="str">
+        <v>Вибуття.Термін</v>
+      </c>
+      <c r="N1" s="59" t="str">
+        <v>Вибуття.Дорога</v>
+      </c>
+      <c r="O1" s="59" t="str">
+        <v>Прибуття.План</v>
+      </c>
+      <c r="P1" s="59" t="str">
+        <v>Прибуття</v>
+      </c>
+      <c r="Q1" s="59" t="str">
+        <v>Прибуття.Продовольче</v>
+      </c>
+      <c r="R1" s="59" t="str">
+        <v>Прибуття.Наказ</v>
+      </c>
+      <c r="S1" s="59" t="str">
+        <v>Вибуття.Підстава</v>
+      </c>
+      <c r="T1" s="59" t="str">
+        <v>Супровідний документ</v>
+      </c>
+      <c r="U1" s="59" t="str">
+        <v>Прибуття.Підстава</v>
+      </c>
+      <c r="V1" s="59" t="str">
+        <v>ТВО.ПІБ</v>
+      </c>
+      <c r="W1" s="59" t="str">
+        <v>ТВО.ІПН</v>
+      </c>
+      <c r="X1" s="59" t="str">
+        <v>ТВО.Посада</v>
+      </c>
+      <c r="Y1" s="59" t="str">
+        <v>Додаткова інформація</v>
+      </c>
+      <c r="Z1" s="59" t="str">
+        <v>Валідація</v>
+      </c>
+      <c r="AA1" s="59" t="str">
+        <v>Статус потенціально незакритих записів</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="61">
+      <c r="A2" s="61" t="str">
+        <v>S05</v>
+      </c>
+      <c r="B2" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G2" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="64" t="s">
-        <v>335</v>
-      </c>
-      <c r="I2" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J2" s="61" t="s">
-        <v>83</v>
+      <c r="C2" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D2" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E2" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F2" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G2" s="63" t="str">
+        <v>Стаціонарне лікування</v>
+      </c>
+      <c r="H2" s="64" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="I2" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J2" s="61" t="str">
+        <v>100</v>
       </c>
       <c r="K2" s="61"/>
-      <c r="L2" s="66">
+      <c r="L2" s="66" t="n">
         <v>46296</v>
       </c>
-      <c r="M2" s="61">
+      <c r="M2" s="61" t="n">
         <v>10</v>
       </c>
       <c r="N2" s="61"/>
-      <c r="O2" s="67">
+      <c r="O2" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P2" s="66"/>
       <c r="Q2" s="61"/>
       <c r="R2" s="61"/>
-      <c r="S2" s="61" t="s">
-        <v>84</v>
+      <c r="S2" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1200-в (ТЕСТ-S05-H01) від 01.10.2026).</v>
       </c>
       <c r="T2" s="61"/>
       <c r="U2" s="61"/>
       <c r="V2" s="61"/>
       <c r="W2" s="61"/>
       <c r="X2" s="61"/>
-      <c r="Y2" s="61" t="s">
-        <v>85</v>
+      <c r="Y2" s="61" t="str">
+        <v>Fixture S05</v>
       </c>
       <c r="Z2" s="61"/>
       <c r="AA2" s="61"/>
     </row>
     <row r="3" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="61">
+      <c r="A3" s="61" t="str">
+        <v>S06</v>
+      </c>
+      <c r="B3" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F3" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="63" t="s">
+      <c r="C3" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D3" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E3" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F3" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G3" s="63" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H3" s="64" t="str">
+        <v>м. Тестоград</v>
+      </c>
+      <c r="I3" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J3" s="61" t="str">
+        <v>100</v>
+      </c>
+      <c r="K3" s="61"/>
+      <c r="L3" s="66" t="n">
+        <v>46296</v>
+      </c>
+      <c r="M3" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="H3" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J3" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="66">
-        <v>46296</v>
-      </c>
-      <c r="M3" s="61">
-        <v>10</v>
-      </c>
       <c r="N3" s="61"/>
-      <c r="O3" s="67">
+      <c r="O3" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P3" s="66"/>
       <c r="Q3" s="61"/>
       <c r="R3" s="61"/>
-      <c r="S3" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="T3" s="61"/>
+      <c r="S3" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1201-в (ТЕСТ-S06-H02) від 01.10.2026).</v>
+      </c>
+      <c r="T3" s="61" t="str">
+        <v>2026/100/7 (ТЕСТ-S06-H02)</v>
+      </c>
       <c r="U3" s="61"/>
       <c r="V3" s="61"/>
       <c r="W3" s="61"/>
       <c r="X3" s="61"/>
-      <c r="Y3" s="61" t="s">
-        <v>87</v>
+      <c r="Y3" s="61" t="str">
+        <v>Fixture S06</v>
       </c>
       <c r="Z3" s="61"/>
       <c r="AA3" s="61"/>
     </row>
     <row r="4" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="61">
+      <c r="A4" s="61" t="str">
+        <v>S07</v>
+      </c>
+      <c r="B4" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F4" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J4" s="61" t="s">
-        <v>83</v>
+      <c r="C4" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D4" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E4" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F4" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G4" s="63" t="str">
+        <v>Відпустка для лікування</v>
+      </c>
+      <c r="H4" s="64" t="str">
+        <v>м. Тестоград</v>
+      </c>
+      <c r="I4" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J4" s="61" t="str">
+        <v>100</v>
       </c>
       <c r="K4" s="61"/>
-      <c r="L4" s="66">
+      <c r="L4" s="66" t="n">
         <v>46296</v>
       </c>
-      <c r="M4" s="61">
+      <c r="M4" s="61" t="n">
         <v>10</v>
       </c>
       <c r="N4" s="61"/>
-      <c r="O4" s="67">
+      <c r="O4" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P4" s="66"/>
       <c r="Q4" s="61"/>
       <c r="R4" s="61"/>
-      <c r="S4" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="T4" s="61"/>
+      <c r="S4" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1202-в (ТЕСТ-S07-H03) від 01.10.2026).</v>
+      </c>
+      <c r="T4" s="61" t="str">
+        <v>2026/100/7 (ТЕСТ-S07-H03)</v>
+      </c>
       <c r="U4" s="61"/>
       <c r="V4" s="61"/>
       <c r="W4" s="61"/>
       <c r="X4" s="61"/>
-      <c r="Y4" s="61" t="s">
-        <v>88</v>
+      <c r="Y4" s="61" t="str">
+        <v>Fixture S07</v>
       </c>
       <c r="Z4" s="61"/>
       <c r="AA4" s="61"/>
     </row>
     <row r="5" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="61" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="61">
+      <c r="A5" s="61" t="str">
+        <v>S08</v>
+      </c>
+      <c r="B5" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F5" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J5" s="61" t="s">
-        <v>83</v>
+      <c r="C5" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D5" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E5" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F5" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G5" s="63" t="str">
+        <v>Відпустка за сімейними обставинами</v>
+      </c>
+      <c r="H5" s="64" t="str">
+        <v>м. Тестоград</v>
+      </c>
+      <c r="I5" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J5" s="61" t="str">
+        <v>100</v>
       </c>
       <c r="K5" s="61"/>
-      <c r="L5" s="66">
+      <c r="L5" s="66" t="n">
         <v>46296</v>
       </c>
-      <c r="M5" s="61">
+      <c r="M5" s="61" t="n">
         <v>10</v>
       </c>
       <c r="N5" s="61"/>
-      <c r="O5" s="67">
+      <c r="O5" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P5" s="66"/>
       <c r="Q5" s="61"/>
       <c r="R5" s="61"/>
-      <c r="S5" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="T5" s="61"/>
+      <c r="S5" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1203-в (ТЕСТ-S08-H04) від 01.10.2026).</v>
+      </c>
+      <c r="T5" s="61" t="str">
+        <v>2026/100/7 (ТЕСТ-S08-H04)</v>
+      </c>
       <c r="U5" s="61"/>
       <c r="V5" s="61"/>
       <c r="W5" s="61"/>
       <c r="X5" s="61"/>
-      <c r="Y5" s="61" t="s">
-        <v>89</v>
+      <c r="Y5" s="61" t="str">
+        <v>Fixture S08</v>
       </c>
       <c r="Z5" s="61"/>
       <c r="AA5" s="61"/>
     </row>
     <row r="6" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="61">
+      <c r="A6" s="61" t="str">
+        <v>S09</v>
+      </c>
+      <c r="B6" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F6" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="63" t="s">
+      <c r="C6" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D6" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E6" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F6" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G6" s="63" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H6" s="64" t="str">
+        <v>м. Тестоград</v>
+      </c>
+      <c r="I6" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J6" s="61" t="str">
+        <v>100</v>
+      </c>
+      <c r="K6" s="61"/>
+      <c r="L6" s="66" t="n">
+        <v>46296</v>
+      </c>
+      <c r="M6" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J6" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="K6" s="61"/>
-      <c r="L6" s="66">
-        <v>46296</v>
-      </c>
-      <c r="M6" s="61">
-        <v>10</v>
-      </c>
       <c r="N6" s="61"/>
-      <c r="O6" s="67">
+      <c r="O6" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P6" s="66"/>
       <c r="Q6" s="61"/>
       <c r="R6" s="61"/>
-      <c r="S6" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="T6" s="61"/>
+      <c r="S6" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1204-в (ТЕСТ-S09-H05) від 01.10.2026).</v>
+      </c>
+      <c r="T6" s="61" t="str">
+        <v>2026/100/7 (ТЕСТ-S09-H05)</v>
+      </c>
       <c r="U6" s="61"/>
       <c r="V6" s="61"/>
       <c r="W6" s="61"/>
       <c r="X6" s="61"/>
-      <c r="Y6" s="61" t="s">
-        <v>90</v>
+      <c r="Y6" s="61" t="str">
+        <v>Fixture S09</v>
       </c>
       <c r="Z6" s="61"/>
       <c r="AA6" s="61"/>
     </row>
     <row r="7" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="61" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="61">
+      <c r="A7" s="61" t="str">
+        <v>S10</v>
+      </c>
+      <c r="B7" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F7" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G7" s="63" t="s">
+      <c r="C7" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D7" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E7" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F7" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G7" s="63" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H7" s="64" t="str">
+        <v>м. Тестоград</v>
+      </c>
+      <c r="I7" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J7" s="61" t="str">
+        <v>100</v>
+      </c>
+      <c r="K7" s="61"/>
+      <c r="L7" s="66" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M7" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="H7" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J7" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="K7" s="61"/>
-      <c r="L7" s="66">
-        <v>46266</v>
-      </c>
-      <c r="M7" s="61">
-        <v>10</v>
-      </c>
       <c r="N7" s="61"/>
-      <c r="O7" s="67">
+      <c r="O7" s="67" t="n">
         <v>46320</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="66" t="n">
         <v>46275</v>
       </c>
       <c r="Q7" s="61"/>
-      <c r="R7" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="S7" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="T7" s="61"/>
-      <c r="U7" s="61" t="s">
-        <v>92</v>
+      <c r="R7" s="61" t="str">
+        <v>110</v>
+      </c>
+      <c r="S7" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1205-в (ТЕСТ-S10-H06) від 01.09.2026).</v>
+      </c>
+      <c r="T7" s="61" t="str">
+        <v>2026/100/7 (ТЕСТ-S10-H06)</v>
+      </c>
+      <c r="U7" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1305-в (ТЕСТ-S10-H06-A) від 10.09.2026).</v>
       </c>
       <c r="V7" s="61"/>
       <c r="W7" s="61"/>
       <c r="X7" s="61"/>
-      <c r="Y7" s="61" t="s">
-        <v>93</v>
+      <c r="Y7" s="61" t="str">
+        <v>Fixture S10</v>
       </c>
       <c r="Z7" s="61"/>
       <c r="AA7" s="61"/>
     </row>
     <row r="8" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="61">
+      <c r="A8" s="61" t="str">
+        <v>S11</v>
+      </c>
+      <c r="B8" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F8" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G8" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="64" t="s">
-        <v>335</v>
-      </c>
-      <c r="I8" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J8" s="61" t="s">
-        <v>83</v>
+      <c r="C8" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D8" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E8" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F8" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G8" s="63" t="str">
+        <v>Стаціонарне лікування</v>
+      </c>
+      <c r="H8" s="64" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="I8" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J8" s="61" t="str">
+        <v>100</v>
       </c>
       <c r="K8" s="61"/>
-      <c r="L8" s="66">
+      <c r="L8" s="66" t="n">
         <v>46296</v>
       </c>
-      <c r="M8" s="61">
+      <c r="M8" s="61" t="n">
         <v>10</v>
       </c>
       <c r="N8" s="61"/>
-      <c r="O8" s="67">
+      <c r="O8" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P8" s="66"/>
       <c r="Q8" s="61"/>
       <c r="R8" s="61"/>
-      <c r="S8" s="61" t="s">
-        <v>84</v>
+      <c r="S8" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1206-в (ТЕСТ-S11-H07) від 01.10.2026).</v>
       </c>
       <c r="T8" s="61"/>
       <c r="U8" s="61"/>
       <c r="V8" s="61"/>
       <c r="W8" s="61"/>
       <c r="X8" s="61"/>
-      <c r="Y8" s="61" t="s">
-        <v>94</v>
+      <c r="Y8" s="61" t="str">
+        <v>Fixture S11</v>
       </c>
       <c r="Z8" s="61"/>
       <c r="AA8" s="61"/>
     </row>
     <row r="9" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="61">
+      <c r="A9" s="61" t="str">
+        <v>S11</v>
+      </c>
+      <c r="B9" s="61" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G9" s="63" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="64" t="s">
-        <v>335</v>
-      </c>
-      <c r="I9" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J9" s="61" t="s">
-        <v>95</v>
+      <c r="C9" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D9" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E9" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F9" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G9" s="63" t="str">
+        <v>Стаціонарне лікування</v>
+      </c>
+      <c r="H9" s="64" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="I9" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J9" s="61" t="str">
+        <v>101</v>
       </c>
       <c r="K9" s="61"/>
-      <c r="L9" s="66">
+      <c r="L9" s="66" t="n">
         <v>46297</v>
       </c>
-      <c r="M9" s="61">
+      <c r="M9" s="61" t="n">
         <v>10</v>
       </c>
       <c r="N9" s="61"/>
-      <c r="O9" s="67">
+      <c r="O9" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P9" s="66"/>
       <c r="Q9" s="61"/>
       <c r="R9" s="61"/>
-      <c r="S9" s="61" t="s">
-        <v>84</v>
+      <c r="S9" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1207-в (ТЕСТ-S11-H08) від 02.10.2026).</v>
       </c>
       <c r="T9" s="61"/>
       <c r="U9" s="61"/>
       <c r="V9" s="61"/>
       <c r="W9" s="61"/>
       <c r="X9" s="61"/>
-      <c r="Y9" s="61" t="s">
-        <v>94</v>
+      <c r="Y9" s="61" t="str">
+        <v>Fixture S11</v>
       </c>
       <c r="Z9" s="61"/>
       <c r="AA9" s="61"/>
     </row>
     <row r="10" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="61">
+      <c r="A10" s="61" t="str">
+        <v>S13</v>
+      </c>
+      <c r="B10" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G10" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J10" s="61" t="s">
-        <v>83</v>
+      <c r="C10" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D10" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E10" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F10" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G10" s="63" t="str">
+        <v>Відпустка для лікування</v>
+      </c>
+      <c r="H10" s="64" t="str">
+        <v>м. Тестоград</v>
+      </c>
+      <c r="I10" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J10" s="61" t="str">
+        <v>100</v>
       </c>
       <c r="K10" s="61"/>
-      <c r="L10" s="66">
+      <c r="L10" s="66" t="n">
         <v>46315</v>
       </c>
-      <c r="M10" s="61">
+      <c r="M10" s="61" t="n">
         <v>10</v>
       </c>
       <c r="N10" s="61"/>
-      <c r="O10" s="67">
+      <c r="O10" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P10" s="66"/>
       <c r="Q10" s="61"/>
       <c r="R10" s="61"/>
-      <c r="S10" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="T10" s="61"/>
+      <c r="S10" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1208-в (ТЕСТ-S13-H09) від 20.10.2026).</v>
+      </c>
+      <c r="T10" s="61" t="str">
+        <v>2026/100/7 (ТЕСТ-S13-H09)</v>
+      </c>
       <c r="U10" s="61"/>
       <c r="V10" s="61"/>
       <c r="W10" s="61"/>
       <c r="X10" s="61"/>
-      <c r="Y10" s="61" t="s">
-        <v>96</v>
+      <c r="Y10" s="61" t="str">
+        <v>Fixture S13</v>
       </c>
       <c r="Z10" s="61"/>
       <c r="AA10" s="61"/>
     </row>
     <row r="11" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="61" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="61">
+      <c r="A11" s="61" t="str">
+        <v>S14</v>
+      </c>
+      <c r="B11" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G11" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J11" s="61" t="s">
-        <v>97</v>
+      <c r="C11" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D11" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E11" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F11" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G11" s="63" t="str">
+        <v>Відпустка за сімейними обставинами</v>
+      </c>
+      <c r="H11" s="64" t="str">
+        <v>м. Тестоград</v>
+      </c>
+      <c r="I11" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J11" s="61" t="str">
+        <v>115</v>
       </c>
       <c r="K11" s="61"/>
-      <c r="L11" s="66">
+      <c r="L11" s="66" t="n">
         <v>46310</v>
       </c>
-      <c r="M11" s="61">
+      <c r="M11" s="61" t="n">
         <v>10</v>
       </c>
       <c r="N11" s="61"/>
-      <c r="O11" s="67">
+      <c r="O11" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P11" s="66"/>
       <c r="Q11" s="61"/>
       <c r="R11" s="61"/>
-      <c r="S11" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="T11" s="61"/>
+      <c r="S11" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1209-в (ТЕСТ-S14-H10) від 15.10.2026).</v>
+      </c>
+      <c r="T11" s="61" t="str">
+        <v>2026/115/7 (ТЕСТ-S14-H10)</v>
+      </c>
       <c r="U11" s="61"/>
       <c r="V11" s="61"/>
       <c r="W11" s="61"/>
       <c r="X11" s="61"/>
-      <c r="Y11" s="61" t="s">
-        <v>98</v>
+      <c r="Y11" s="61" t="str">
+        <v>Fixture S14</v>
       </c>
       <c r="Z11" s="61"/>
       <c r="AA11" s="61"/>
     </row>
     <row r="12" spans="1:27" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="61">
+      <c r="A12" s="61" t="str">
+        <v>S15</v>
+      </c>
+      <c r="B12" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="63" t="s">
+      <c r="C12" s="61" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D12" s="61" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E12" s="62" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F12" s="61" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G12" s="63" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H12" s="64" t="str">
+        <v>м. Тестоград</v>
+      </c>
+      <c r="I12" s="65" t="str">
+        <v>Так</v>
+      </c>
+      <c r="J12" s="61" t="str">
+        <v>100</v>
+      </c>
+      <c r="K12" s="61"/>
+      <c r="L12" s="66" t="n">
+        <v>46296</v>
+      </c>
+      <c r="M12" s="61" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="J12" s="61" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="61"/>
-      <c r="L12" s="66">
-        <v>46296</v>
-      </c>
-      <c r="M12" s="61">
-        <v>10</v>
-      </c>
       <c r="N12" s="61"/>
-      <c r="O12" s="67">
+      <c r="O12" s="67" t="n">
         <v>46320</v>
       </c>
       <c r="P12" s="66"/>
       <c r="Q12" s="61"/>
       <c r="R12" s="61"/>
-      <c r="S12" s="61" t="s">
-        <v>84</v>
-      </c>
-      <c r="T12" s="61"/>
+      <c r="S12" s="61" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1210-в (ТЕСТ-S15-H11) від 01.10.2026).</v>
+      </c>
+      <c r="T12" s="61" t="str">
+        <v>2026/100/7 (ТЕСТ-S15-H11)</v>
+      </c>
       <c r="U12" s="61"/>
       <c r="V12" s="61"/>
       <c r="W12" s="61"/>
       <c r="X12" s="61"/>
-      <c r="Y12" s="61" t="s">
-        <v>99</v>
+      <c r="Y12" s="61" t="str">
+        <v>Fixture S15</v>
       </c>
       <c r="Z12" s="61"/>
       <c r="AA12" s="61"/>
@@ -35492,139 +35508,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="C1" s="48" t="s">
-        <v>267</v>
-      </c>
-      <c r="D1" s="48" t="s">
-        <v>268</v>
-      </c>
-      <c r="E1" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="48" t="s">
-        <v>196</v>
-      </c>
-      <c r="H1" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="I1" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="J1" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="K1" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="L1" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="M1" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="N1" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="O1" s="48" t="s">
-        <v>202</v>
-      </c>
-      <c r="P1" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q1" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="R1" s="48" t="s">
-        <v>205</v>
-      </c>
-      <c r="S1" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="T1" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="U1" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="V1" s="48" t="s">
-        <v>211</v>
-      </c>
-      <c r="W1" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="X1" s="48" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y1" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z1" s="48" t="s">
-        <v>334</v>
+      <c r="A1" s="48" t="str">
+        <v>ScenarioId</v>
+      </c>
+      <c r="B1" s="48" t="str">
+        <v>StepId</v>
+      </c>
+      <c r="C1" s="48" t="str">
+        <v>StepOrder</v>
+      </c>
+      <c r="D1" s="48" t="str">
+        <v>Action</v>
+      </c>
+      <c r="E1" s="48" t="str">
+        <v>ModeId</v>
+      </c>
+      <c r="F1" s="48" t="str">
+        <v>AcceptedOrderNumber</v>
+      </c>
+      <c r="G1" s="48" t="str">
+        <v>AcceptedOrderDate</v>
+      </c>
+      <c r="H1" s="48" t="str">
+        <v>Destination</v>
+      </c>
+      <c r="I1" s="48" t="str">
+        <v>Hospital</v>
+      </c>
+      <c r="J1" s="48" t="str">
+        <v>HospitalShortName</v>
+      </c>
+      <c r="K1" s="48" t="str">
+        <v>PersonRank</v>
+      </c>
+      <c r="L1" s="48" t="str">
+        <v>PersonName</v>
+      </c>
+      <c r="M1" s="48" t="str">
+        <v>PersonId</v>
+      </c>
+      <c r="N1" s="48" t="str">
+        <v>PositionCode</v>
+      </c>
+      <c r="O1" s="48" t="str">
+        <v>ReportRank</v>
+      </c>
+      <c r="P1" s="48" t="str">
+        <v>ReportName</v>
+      </c>
+      <c r="Q1" s="48" t="str">
+        <v>ReportPositionCode</v>
+      </c>
+      <c r="R1" s="48" t="str">
+        <v>IncomingNumber</v>
+      </c>
+      <c r="S1" s="48" t="str">
+        <v>IncomingDate</v>
+      </c>
+      <c r="T1" s="48" t="str">
+        <v>Document</v>
+      </c>
+      <c r="U1" s="48" t="str">
+        <v>DocumentDate</v>
+      </c>
+      <c r="V1" s="48" t="str">
+        <v>DocumentNumber</v>
+      </c>
+      <c r="W1" s="48" t="str">
+        <v>EventDate</v>
+      </c>
+      <c r="X1" s="48" t="str">
+        <v>TicketNumber</v>
+      </c>
+      <c r="Y1" s="48" t="str">
+        <v>TicketDate</v>
+      </c>
+      <c r="Z1" s="48" t="str">
+        <v>Notes</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="57" t="s">
-        <v>269</v>
-      </c>
-      <c r="C2" s="57">
+      <c r="A2" s="57" t="str">
+        <v>S01</v>
+      </c>
+      <c r="B2" s="57" t="str">
+        <v>S01-M01</v>
+      </c>
+      <c r="C2" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E2" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="56">
+      <c r="D2" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E2" s="57" t="str">
+        <v>ToHospital</v>
+      </c>
+      <c r="F2" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G2" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H2" s="57"/>
-      <c r="I2" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="J2" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K2" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L2" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N2" s="57" t="s">
-        <v>134</v>
+      <c r="I2" s="57" t="str">
+        <v>Комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради</v>
+      </c>
+      <c r="J2" s="57" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="K2" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L2" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M2" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N2" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O2" s="57"/>
       <c r="P2" s="57"/>
       <c r="Q2" s="57"/>
-      <c r="R2" s="57" t="s">
-        <v>228</v>
-      </c>
-      <c r="S2" s="56">
+      <c r="R2" s="57" t="str">
+        <v>1656/1234-в (ТЕСТ-S01-1)</v>
+      </c>
+      <c r="S2" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T2" s="57"/>
       <c r="U2" s="56"/>
       <c r="V2" s="57"/>
-      <c r="W2" s="56">
+      <c r="W2" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="X2" s="57"/>
@@ -35632,245 +35648,245 @@
       <c r="Z2" s="57"/>
     </row>
     <row r="3" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>272</v>
-      </c>
-      <c r="C3" s="57">
+      <c r="A3" s="57" t="str">
+        <v>S02</v>
+      </c>
+      <c r="B3" s="57" t="str">
+        <v>S02-M01</v>
+      </c>
+      <c r="C3" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>339</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G3" s="56">
+      <c r="D3" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E3" s="57" t="str">
+        <v>ToAnnualMainVacation</v>
+      </c>
+      <c r="F3" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G3" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H3" s="57" t="s">
-        <v>86</v>
+      <c r="H3" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I3" s="57"/>
       <c r="J3" s="57"/>
-      <c r="K3" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L3" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N3" s="57" t="s">
-        <v>134</v>
+      <c r="K3" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L3" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M3" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N3" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O3" s="57"/>
       <c r="P3" s="57"/>
       <c r="Q3" s="57"/>
-      <c r="R3" s="57" t="s">
-        <v>230</v>
-      </c>
-      <c r="S3" s="56">
+      <c r="R3" s="57" t="str">
+        <v>1656/1235-в (ТЕСТ-S02-1)</v>
+      </c>
+      <c r="S3" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T3" s="57"/>
       <c r="U3" s="56"/>
       <c r="V3" s="57"/>
-      <c r="W3" s="56">
+      <c r="W3" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X3" s="57" t="s">
-        <v>230</v>
-      </c>
-      <c r="Y3" s="56">
+      <c r="X3" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S02-1)</v>
+      </c>
+      <c r="Y3" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z3" s="57"/>
     </row>
     <row r="4" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>274</v>
-      </c>
-      <c r="C4" s="57">
+      <c r="A4" s="57" t="str">
+        <v>S03</v>
+      </c>
+      <c r="B4" s="57" t="str">
+        <v>S03-M01</v>
+      </c>
+      <c r="C4" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>340</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G4" s="56">
+      <c r="D4" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E4" s="57" t="str">
+        <v>ToVacationForCuring</v>
+      </c>
+      <c r="F4" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G4" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H4" s="57" t="s">
-        <v>86</v>
+      <c r="H4" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I4" s="57"/>
       <c r="J4" s="57"/>
-      <c r="K4" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L4" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N4" s="57" t="s">
-        <v>134</v>
+      <c r="K4" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L4" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M4" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N4" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O4" s="57"/>
       <c r="P4" s="57"/>
       <c r="Q4" s="57"/>
-      <c r="R4" s="57" t="s">
-        <v>232</v>
-      </c>
-      <c r="S4" s="56">
+      <c r="R4" s="57" t="str">
+        <v>1656/1236-в (ТЕСТ-S03-1)</v>
+      </c>
+      <c r="S4" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T4" s="57"/>
       <c r="U4" s="56"/>
       <c r="V4" s="57"/>
-      <c r="W4" s="56">
+      <c r="W4" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X4" s="57" t="s">
-        <v>232</v>
-      </c>
-      <c r="Y4" s="56">
+      <c r="X4" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S03-1)</v>
+      </c>
+      <c r="Y4" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z4" s="57"/>
     </row>
     <row r="5" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>276</v>
-      </c>
-      <c r="C5" s="57">
+      <c r="A5" s="57" t="str">
+        <v>S04</v>
+      </c>
+      <c r="B5" s="57" t="str">
+        <v>S04-M01</v>
+      </c>
+      <c r="C5" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>341</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" s="56">
+      <c r="D5" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E5" s="57" t="str">
+        <v>ToVacationForFamily</v>
+      </c>
+      <c r="F5" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G5" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H5" s="57" t="s">
-        <v>86</v>
+      <c r="H5" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I5" s="57"/>
       <c r="J5" s="57"/>
-      <c r="K5" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L5" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N5" s="57" t="s">
-        <v>134</v>
+      <c r="K5" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L5" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M5" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N5" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="57"/>
       <c r="Q5" s="57"/>
-      <c r="R5" s="57" t="s">
-        <v>234</v>
-      </c>
-      <c r="S5" s="56">
+      <c r="R5" s="57" t="str">
+        <v>1656/1237-в (ТЕСТ-S04-1)</v>
+      </c>
+      <c r="S5" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T5" s="57"/>
       <c r="U5" s="56"/>
       <c r="V5" s="57"/>
-      <c r="W5" s="56">
+      <c r="W5" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X5" s="57" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y5" s="56">
+      <c r="X5" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S04-1)</v>
+      </c>
+      <c r="Y5" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z5" s="57"/>
     </row>
     <row r="6" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="C6" s="57">
+      <c r="A6" s="57" t="str">
+        <v>S05</v>
+      </c>
+      <c r="B6" s="57" t="str">
+        <v>S05-M01</v>
+      </c>
+      <c r="C6" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E6" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="F6" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="56">
+      <c r="D6" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E6" s="57" t="str">
+        <v>FromHospital</v>
+      </c>
+      <c r="F6" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G6" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H6" s="57"/>
-      <c r="I6" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="J6" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K6" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L6" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N6" s="57" t="s">
-        <v>134</v>
+      <c r="I6" s="57" t="str">
+        <v>Комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради</v>
+      </c>
+      <c r="J6" s="57" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="K6" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L6" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M6" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N6" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O6" s="57"/>
       <c r="P6" s="57"/>
       <c r="Q6" s="57"/>
-      <c r="R6" s="57" t="s">
-        <v>229</v>
-      </c>
-      <c r="S6" s="56">
+      <c r="R6" s="57" t="str">
+        <v>1656/1238-в (ТЕСТ-S05-1)</v>
+      </c>
+      <c r="S6" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T6" s="57"/>
       <c r="U6" s="56"/>
       <c r="V6" s="57"/>
-      <c r="W6" s="56">
+      <c r="W6" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="X6" s="57"/>
@@ -35878,307 +35894,307 @@
       <c r="Z6" s="57"/>
     </row>
     <row r="7" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="57" t="s">
-        <v>273</v>
-      </c>
-      <c r="C7" s="57">
+      <c r="A7" s="57" t="str">
+        <v>S06</v>
+      </c>
+      <c r="B7" s="57" t="str">
+        <v>S06-M01</v>
+      </c>
+      <c r="C7" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E7" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="F7" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="56">
+      <c r="D7" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E7" s="57" t="str">
+        <v>FromAnnualMainVacation</v>
+      </c>
+      <c r="F7" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G7" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H7" s="57" t="s">
-        <v>86</v>
+      <c r="H7" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I7" s="57"/>
       <c r="J7" s="57"/>
-      <c r="K7" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L7" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" s="57" t="s">
-        <v>134</v>
+      <c r="K7" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L7" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M7" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N7" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O7" s="57"/>
       <c r="P7" s="57"/>
       <c r="Q7" s="57"/>
-      <c r="R7" s="57" t="s">
-        <v>231</v>
-      </c>
-      <c r="S7" s="56">
+      <c r="R7" s="57" t="str">
+        <v>1656/1239-в (ТЕСТ-S06-1)</v>
+      </c>
+      <c r="S7" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T7" s="57"/>
       <c r="U7" s="56"/>
       <c r="V7" s="57"/>
-      <c r="W7" s="56">
+      <c r="W7" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X7" s="57" t="s">
-        <v>231</v>
-      </c>
-      <c r="Y7" s="56">
+      <c r="X7" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S06-1)</v>
+      </c>
+      <c r="Y7" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z7" s="57"/>
     </row>
     <row r="8" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8" s="57">
+      <c r="A8" s="57" t="str">
+        <v>S07</v>
+      </c>
+      <c r="B8" s="57" t="str">
+        <v>S07-M01</v>
+      </c>
+      <c r="C8" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E8" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="F8" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="56">
+      <c r="D8" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E8" s="57" t="str">
+        <v>FromVacationForCuring</v>
+      </c>
+      <c r="F8" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G8" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H8" s="57" t="s">
-        <v>86</v>
+      <c r="H8" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I8" s="57"/>
       <c r="J8" s="57"/>
-      <c r="K8" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L8" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N8" s="57" t="s">
-        <v>134</v>
+      <c r="K8" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L8" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M8" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N8" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O8" s="57"/>
       <c r="P8" s="57"/>
       <c r="Q8" s="57"/>
-      <c r="R8" s="57" t="s">
-        <v>233</v>
-      </c>
-      <c r="S8" s="56">
+      <c r="R8" s="57" t="str">
+        <v>1656/1240-в (ТЕСТ-S07-1)</v>
+      </c>
+      <c r="S8" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T8" s="57"/>
       <c r="U8" s="56"/>
       <c r="V8" s="57"/>
-      <c r="W8" s="56">
+      <c r="W8" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X8" s="57" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y8" s="56">
+      <c r="X8" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S07-1)</v>
+      </c>
+      <c r="Y8" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z8" s="57"/>
     </row>
     <row r="9" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="57" t="s">
-        <v>277</v>
-      </c>
-      <c r="C9" s="57">
+      <c r="A9" s="57" t="str">
+        <v>S08</v>
+      </c>
+      <c r="B9" s="57" t="str">
+        <v>S08-M01</v>
+      </c>
+      <c r="C9" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E9" s="57" t="s">
-        <v>345</v>
-      </c>
-      <c r="F9" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="56">
+      <c r="D9" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E9" s="57" t="str">
+        <v>FromVacationForFamily</v>
+      </c>
+      <c r="F9" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G9" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H9" s="57" t="s">
-        <v>86</v>
+      <c r="H9" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I9" s="57"/>
       <c r="J9" s="57"/>
-      <c r="K9" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L9" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N9" s="57" t="s">
-        <v>134</v>
+      <c r="K9" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L9" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M9" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N9" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O9" s="57"/>
       <c r="P9" s="57"/>
       <c r="Q9" s="57"/>
-      <c r="R9" s="57" t="s">
-        <v>235</v>
-      </c>
-      <c r="S9" s="56">
+      <c r="R9" s="57" t="str">
+        <v>1656/1241-в (ТЕСТ-S08-1)</v>
+      </c>
+      <c r="S9" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T9" s="57"/>
       <c r="U9" s="56"/>
       <c r="V9" s="57"/>
-      <c r="W9" s="56">
+      <c r="W9" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X9" s="57" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y9" s="56">
+      <c r="X9" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S08-1)</v>
+      </c>
+      <c r="Y9" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z9" s="57"/>
     </row>
     <row r="10" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>278</v>
-      </c>
-      <c r="C10" s="57">
+      <c r="A10" s="57" t="str">
+        <v>S09</v>
+      </c>
+      <c r="B10" s="57" t="str">
+        <v>S09-M01</v>
+      </c>
+      <c r="C10" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E10" s="57" t="s">
-        <v>339</v>
-      </c>
-      <c r="F10" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" s="56">
+      <c r="D10" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E10" s="57" t="str">
+        <v>ToAnnualMainVacation</v>
+      </c>
+      <c r="F10" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G10" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H10" s="57" t="s">
-        <v>86</v>
+      <c r="H10" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
-      <c r="K10" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L10" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N10" s="57" t="s">
-        <v>134</v>
+      <c r="K10" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L10" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M10" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N10" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O10" s="57"/>
       <c r="P10" s="57"/>
       <c r="Q10" s="57"/>
-      <c r="R10" s="57" t="s">
-        <v>236</v>
-      </c>
-      <c r="S10" s="56">
+      <c r="R10" s="57" t="str">
+        <v>1656/1242-в (ТЕСТ-S09-1)</v>
+      </c>
+      <c r="S10" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T10" s="57"/>
       <c r="U10" s="56"/>
       <c r="V10" s="57"/>
-      <c r="W10" s="56">
+      <c r="W10" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X10" s="57" t="s">
-        <v>236</v>
-      </c>
-      <c r="Y10" s="56">
+      <c r="X10" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S09-1)</v>
+      </c>
+      <c r="Y10" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z10" s="57"/>
     </row>
     <row r="11" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="57" t="s">
-        <v>279</v>
-      </c>
-      <c r="C11" s="57">
+      <c r="A11" s="57" t="str">
+        <v>S10</v>
+      </c>
+      <c r="B11" s="57" t="str">
+        <v>S10-M01</v>
+      </c>
+      <c r="C11" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E11" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="56">
+      <c r="D11" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E11" s="57" t="str">
+        <v>ToHospital</v>
+      </c>
+      <c r="F11" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G11" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H11" s="57"/>
-      <c r="I11" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="J11" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K11" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L11" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N11" s="57" t="s">
-        <v>134</v>
+      <c r="I11" s="57" t="str">
+        <v>Комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради</v>
+      </c>
+      <c r="J11" s="57" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="K11" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L11" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M11" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N11" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O11" s="57"/>
       <c r="P11" s="57"/>
       <c r="Q11" s="57"/>
-      <c r="R11" s="57" t="s">
-        <v>237</v>
-      </c>
-      <c r="S11" s="56">
+      <c r="R11" s="57" t="str">
+        <v>1656/1243-в (ТЕСТ-S10-1)</v>
+      </c>
+      <c r="S11" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T11" s="57"/>
       <c r="U11" s="56"/>
       <c r="V11" s="57"/>
-      <c r="W11" s="56">
+      <c r="W11" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="X11" s="57"/>
@@ -36186,59 +36202,59 @@
       <c r="Z11" s="57"/>
     </row>
     <row r="12" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>280</v>
-      </c>
-      <c r="C12" s="57">
+      <c r="A12" s="57" t="str">
+        <v>S11</v>
+      </c>
+      <c r="B12" s="57" t="str">
+        <v>S11-M01</v>
+      </c>
+      <c r="C12" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="56">
+      <c r="D12" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E12" s="57" t="str">
+        <v>FromHospital</v>
+      </c>
+      <c r="F12" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G12" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H12" s="57"/>
-      <c r="I12" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="J12" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K12" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L12" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N12" s="57" t="s">
-        <v>134</v>
+      <c r="I12" s="57" t="str">
+        <v>Комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради</v>
+      </c>
+      <c r="J12" s="57" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="K12" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L12" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M12" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N12" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O12" s="57"/>
       <c r="P12" s="57"/>
       <c r="Q12" s="57"/>
-      <c r="R12" s="57" t="s">
-        <v>238</v>
-      </c>
-      <c r="S12" s="56">
+      <c r="R12" s="57" t="str">
+        <v>1656/1244-в (ТЕСТ-S11-1)</v>
+      </c>
+      <c r="S12" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T12" s="57"/>
       <c r="U12" s="56"/>
       <c r="V12" s="57"/>
-      <c r="W12" s="56">
+      <c r="W12" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="X12" s="57"/>
@@ -36246,431 +36262,431 @@
       <c r="Z12" s="57"/>
     </row>
     <row r="13" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="57" t="s">
-        <v>281</v>
-      </c>
-      <c r="C13" s="57">
+      <c r="A13" s="57" t="str">
+        <v>S12</v>
+      </c>
+      <c r="B13" s="57" t="str">
+        <v>S12-M01</v>
+      </c>
+      <c r="C13" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E13" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="F13" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="56">
+      <c r="D13" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E13" s="57" t="str">
+        <v>FromAnnualMainVacation</v>
+      </c>
+      <c r="F13" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G13" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H13" s="57" t="s">
-        <v>86</v>
+      <c r="H13" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I13" s="57"/>
       <c r="J13" s="57"/>
-      <c r="K13" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L13" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M13" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N13" s="57" t="s">
-        <v>134</v>
+      <c r="K13" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L13" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M13" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N13" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O13" s="57"/>
       <c r="P13" s="57"/>
       <c r="Q13" s="57"/>
-      <c r="R13" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="S13" s="56">
+      <c r="R13" s="57" t="str">
+        <v>1656/1245-в (ТЕСТ-S12-1)</v>
+      </c>
+      <c r="S13" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T13" s="57"/>
       <c r="U13" s="56"/>
       <c r="V13" s="57"/>
-      <c r="W13" s="56">
+      <c r="W13" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X13" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="Y13" s="56">
+      <c r="X13" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S12-1)</v>
+      </c>
+      <c r="Y13" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z13" s="57"/>
     </row>
     <row r="14" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="57" t="s">
-        <v>282</v>
-      </c>
-      <c r="C14" s="57">
+      <c r="A14" s="57" t="str">
+        <v>S13</v>
+      </c>
+      <c r="B14" s="57" t="str">
+        <v>S13-M01</v>
+      </c>
+      <c r="C14" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="F14" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="56">
+      <c r="D14" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E14" s="57" t="str">
+        <v>FromVacationForCuring</v>
+      </c>
+      <c r="F14" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G14" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H14" s="57" t="s">
-        <v>86</v>
+      <c r="H14" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I14" s="57"/>
       <c r="J14" s="57"/>
-      <c r="K14" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L14" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M14" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N14" s="57" t="s">
-        <v>134</v>
+      <c r="K14" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L14" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M14" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N14" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O14" s="57"/>
       <c r="P14" s="57"/>
       <c r="Q14" s="57"/>
-      <c r="R14" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="S14" s="56">
+      <c r="R14" s="57" t="str">
+        <v>1656/1246-в (ТЕСТ-S13-1)</v>
+      </c>
+      <c r="S14" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T14" s="57"/>
       <c r="U14" s="56"/>
       <c r="V14" s="57"/>
-      <c r="W14" s="56">
+      <c r="W14" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X14" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y14" s="56">
+      <c r="X14" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S13-1)</v>
+      </c>
+      <c r="Y14" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z14" s="57"/>
     </row>
     <row r="15" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="57" t="s">
-        <v>283</v>
-      </c>
-      <c r="C15" s="57">
+      <c r="A15" s="57" t="str">
+        <v>S14</v>
+      </c>
+      <c r="B15" s="57" t="str">
+        <v>S14-M01</v>
+      </c>
+      <c r="C15" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E15" s="57" t="s">
-        <v>341</v>
-      </c>
-      <c r="F15" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="56">
+      <c r="D15" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E15" s="57" t="str">
+        <v>ToVacationForFamily</v>
+      </c>
+      <c r="F15" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G15" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H15" s="57" t="s">
-        <v>86</v>
+      <c r="H15" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I15" s="57"/>
       <c r="J15" s="57"/>
-      <c r="K15" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L15" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M15" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N15" s="57" t="s">
-        <v>134</v>
+      <c r="K15" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L15" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M15" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N15" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O15" s="57"/>
       <c r="P15" s="57"/>
       <c r="Q15" s="57"/>
-      <c r="R15" s="57" t="s">
-        <v>241</v>
-      </c>
-      <c r="S15" s="56">
+      <c r="R15" s="57" t="str">
+        <v>1656/1247-в (ТЕСТ-S14-1)</v>
+      </c>
+      <c r="S15" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T15" s="57"/>
       <c r="U15" s="56"/>
       <c r="V15" s="57"/>
-      <c r="W15" s="56">
+      <c r="W15" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X15" s="57" t="s">
-        <v>241</v>
-      </c>
-      <c r="Y15" s="56">
+      <c r="X15" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S14-1)</v>
+      </c>
+      <c r="Y15" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z15" s="57"/>
     </row>
     <row r="16" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="57" t="s">
-        <v>284</v>
-      </c>
-      <c r="C16" s="57">
+      <c r="A16" s="57" t="str">
+        <v>S15</v>
+      </c>
+      <c r="B16" s="57" t="str">
+        <v>S15-M01</v>
+      </c>
+      <c r="C16" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="F16" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="56">
+      <c r="D16" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E16" s="57" t="str">
+        <v>ToHospital</v>
+      </c>
+      <c r="F16" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G16" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H16" s="57"/>
-      <c r="I16" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="J16" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K16" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L16" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M16" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N16" s="57" t="s">
-        <v>134</v>
+      <c r="I16" s="57" t="str">
+        <v>Комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради</v>
+      </c>
+      <c r="J16" s="57" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="K16" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L16" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M16" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N16" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O16" s="57"/>
       <c r="P16" s="57"/>
       <c r="Q16" s="57"/>
-      <c r="R16" s="57" t="s">
-        <v>242</v>
-      </c>
-      <c r="S16" s="56">
+      <c r="R16" s="57" t="str">
+        <v>1656/1248-в (ТЕСТ-S15-1)</v>
+      </c>
+      <c r="S16" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T16" s="57"/>
       <c r="U16" s="56"/>
       <c r="V16" s="57"/>
-      <c r="W16" s="56">
+      <c r="W16" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="X16" s="57"/>
       <c r="Y16" s="56"/>
-      <c r="Z16" s="57" t="s">
-        <v>132</v>
+      <c r="Z16" s="57" t="str">
+        <v>Очікування навмисно не визначено</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="57" t="s">
-        <v>285</v>
-      </c>
-      <c r="C17" s="57">
+      <c r="A17" s="57" t="str">
+        <v>S16</v>
+      </c>
+      <c r="B17" s="57" t="str">
+        <v>S16-M01</v>
+      </c>
+      <c r="C17" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E17" s="57" t="s">
-        <v>339</v>
-      </c>
-      <c r="F17" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="56">
+      <c r="D17" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E17" s="57" t="str">
+        <v>ToAnnualMainVacation</v>
+      </c>
+      <c r="F17" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G17" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H17" s="57" t="s">
-        <v>86</v>
+      <c r="H17" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I17" s="57"/>
       <c r="J17" s="57"/>
-      <c r="K17" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L17" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M17" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N17" s="57" t="s">
-        <v>134</v>
+      <c r="K17" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L17" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M17" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N17" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O17" s="57"/>
       <c r="P17" s="57"/>
       <c r="Q17" s="57"/>
-      <c r="R17" s="57" t="s">
-        <v>243</v>
-      </c>
-      <c r="S17" s="56">
+      <c r="R17" s="57" t="str">
+        <v>1656/1249-в (ТЕСТ-S16-1)</v>
+      </c>
+      <c r="S17" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T17" s="57"/>
       <c r="U17" s="56"/>
       <c r="V17" s="57"/>
-      <c r="W17" s="56">
+      <c r="W17" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X17" s="57" t="s">
-        <v>243</v>
-      </c>
-      <c r="Y17" s="56">
+      <c r="X17" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S16-1)</v>
+      </c>
+      <c r="Y17" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z17" s="57"/>
     </row>
     <row r="18" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="57">
+      <c r="A18" s="57" t="str">
+        <v>S16</v>
+      </c>
+      <c r="B18" s="57" t="str">
+        <v>S16-M02</v>
+      </c>
+      <c r="C18" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E18" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="56">
+      <c r="D18" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E18" s="57" t="str">
+        <v>FromAnnualMainVacation</v>
+      </c>
+      <c r="F18" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G18" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H18" s="57" t="s">
-        <v>86</v>
+      <c r="H18" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I18" s="57"/>
       <c r="J18" s="57"/>
-      <c r="K18" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L18" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M18" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N18" s="57" t="s">
-        <v>134</v>
+      <c r="K18" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L18" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M18" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N18" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O18" s="57"/>
       <c r="P18" s="57"/>
       <c r="Q18" s="57"/>
-      <c r="R18" s="57" t="s">
-        <v>244</v>
-      </c>
-      <c r="S18" s="56">
+      <c r="R18" s="57" t="str">
+        <v>1656/1250-в (ТЕСТ-S16-2)</v>
+      </c>
+      <c r="S18" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="T18" s="57"/>
       <c r="U18" s="56"/>
       <c r="V18" s="57"/>
-      <c r="W18" s="56">
+      <c r="W18" s="56" t="n">
         <v>46315</v>
       </c>
-      <c r="X18" s="57" t="s">
-        <v>244</v>
-      </c>
-      <c r="Y18" s="56">
+      <c r="X18" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-S16-1)</v>
+      </c>
+      <c r="Y18" s="56" t="n">
         <v>46315</v>
       </c>
       <c r="Z18" s="57"/>
     </row>
     <row r="19" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="57" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="57" t="s">
-        <v>287</v>
-      </c>
-      <c r="C19" s="57">
+      <c r="A19" s="57" t="str">
+        <v>S16</v>
+      </c>
+      <c r="B19" s="57" t="str">
+        <v>S16-M03</v>
+      </c>
+      <c r="C19" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E19" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="F19" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="56">
+      <c r="D19" s="57" t="str">
+        <v>ExportMovement</v>
+      </c>
+      <c r="E19" s="57" t="str">
+        <v>ToHospital</v>
+      </c>
+      <c r="F19" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G19" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H19" s="57"/>
-      <c r="I19" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="J19" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K19" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L19" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M19" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N19" s="57" t="s">
-        <v>134</v>
+      <c r="I19" s="57" t="str">
+        <v>Комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради</v>
+      </c>
+      <c r="J19" s="57" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="K19" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L19" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M19" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N19" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O19" s="57"/>
       <c r="P19" s="57"/>
       <c r="Q19" s="57"/>
-      <c r="R19" s="57" t="s">
-        <v>245</v>
-      </c>
-      <c r="S19" s="56">
+      <c r="R19" s="57" t="str">
+        <v>1656/1251-в (ТЕСТ-S16-3)</v>
+      </c>
+      <c r="S19" s="56" t="n">
         <v>46316</v>
       </c>
       <c r="T19" s="57"/>
       <c r="U19" s="56"/>
       <c r="V19" s="57"/>
-      <c r="W19" s="56">
+      <c r="W19" s="56" t="n">
         <v>46316</v>
       </c>
       <c r="X19" s="57"/>
@@ -36678,59 +36694,59 @@
       <c r="Z19" s="57"/>
     </row>
     <row r="20" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57" t="s">
-        <v>247</v>
-      </c>
-      <c r="B20" s="57" t="s">
-        <v>288</v>
-      </c>
-      <c r="C20" s="57">
+      <c r="A20" s="57" t="str">
+        <v>W01</v>
+      </c>
+      <c r="B20" s="57" t="str">
+        <v>W01-P01</v>
+      </c>
+      <c r="C20" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E20" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="F20" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" s="56">
+      <c r="D20" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E20" s="57" t="str">
+        <v>ToHospital</v>
+      </c>
+      <c r="F20" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G20" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H20" s="57"/>
-      <c r="I20" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="J20" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K20" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L20" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M20" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N20" s="57" t="s">
-        <v>134</v>
+      <c r="I20" s="57" t="str">
+        <v>Комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради</v>
+      </c>
+      <c r="J20" s="57" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="K20" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L20" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M20" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N20" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O20" s="57"/>
       <c r="P20" s="57"/>
       <c r="Q20" s="57"/>
-      <c r="R20" s="57" t="s">
-        <v>289</v>
-      </c>
-      <c r="S20" s="56">
+      <c r="R20" s="57" t="str">
+        <v>1656/1252-в (ТЕСТ-W01)</v>
+      </c>
+      <c r="S20" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T20" s="57"/>
       <c r="U20" s="56"/>
       <c r="V20" s="57"/>
-      <c r="W20" s="56">
+      <c r="W20" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="X20" s="57"/>
@@ -36738,59 +36754,59 @@
       <c r="Z20" s="57"/>
     </row>
     <row r="21" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57" t="s">
-        <v>251</v>
-      </c>
-      <c r="B21" s="57" t="s">
-        <v>290</v>
-      </c>
-      <c r="C21" s="57">
+      <c r="A21" s="57" t="str">
+        <v>W02</v>
+      </c>
+      <c r="B21" s="57" t="str">
+        <v>W02-P01</v>
+      </c>
+      <c r="C21" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E21" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="F21" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="56">
+      <c r="D21" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E21" s="57" t="str">
+        <v>FromHospital</v>
+      </c>
+      <c r="F21" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G21" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H21" s="57"/>
-      <c r="I21" s="57" t="s">
-        <v>333</v>
-      </c>
-      <c r="J21" s="57" t="s">
-        <v>335</v>
-      </c>
-      <c r="K21" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L21" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M21" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N21" s="57" t="s">
-        <v>134</v>
+      <c r="I21" s="57" t="str">
+        <v>Комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради</v>
+      </c>
+      <c r="J21" s="57" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
+      </c>
+      <c r="K21" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L21" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M21" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N21" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O21" s="57"/>
       <c r="P21" s="57"/>
       <c r="Q21" s="57"/>
-      <c r="R21" s="57" t="s">
-        <v>291</v>
-      </c>
-      <c r="S21" s="56">
+      <c r="R21" s="57" t="str">
+        <v>1656/1253-в (ТЕСТ-W02)</v>
+      </c>
+      <c r="S21" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T21" s="57"/>
       <c r="U21" s="56"/>
       <c r="V21" s="57"/>
-      <c r="W21" s="56">
+      <c r="W21" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="X21" s="57"/>
@@ -36798,429 +36814,429 @@
       <c r="Z21" s="57"/>
     </row>
     <row r="22" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="B22" s="57" t="s">
-        <v>292</v>
-      </c>
-      <c r="C22" s="57">
+      <c r="A22" s="57" t="str">
+        <v>W03</v>
+      </c>
+      <c r="B22" s="57" t="str">
+        <v>W03-P01</v>
+      </c>
+      <c r="C22" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E22" s="57" t="s">
-        <v>339</v>
-      </c>
-      <c r="F22" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G22" s="56">
+      <c r="D22" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E22" s="57" t="str">
+        <v>ToAnnualMainVacation</v>
+      </c>
+      <c r="F22" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G22" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H22" s="57" t="s">
-        <v>86</v>
+      <c r="H22" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I22" s="57"/>
       <c r="J22" s="57"/>
-      <c r="K22" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L22" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M22" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N22" s="57" t="s">
-        <v>134</v>
+      <c r="K22" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L22" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M22" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N22" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O22" s="57"/>
       <c r="P22" s="57"/>
       <c r="Q22" s="57"/>
-      <c r="R22" s="57" t="s">
-        <v>293</v>
-      </c>
-      <c r="S22" s="56">
+      <c r="R22" s="57" t="str">
+        <v>1656/1254-в (ТЕСТ-W03)</v>
+      </c>
+      <c r="S22" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T22" s="57"/>
       <c r="U22" s="56"/>
       <c r="V22" s="57"/>
-      <c r="W22" s="56">
+      <c r="W22" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X22" s="57" t="s">
-        <v>293</v>
-      </c>
-      <c r="Y22" s="56">
+      <c r="X22" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-W03)</v>
+      </c>
+      <c r="Y22" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z22" s="57"/>
     </row>
     <row r="23" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="57" t="s">
-        <v>255</v>
-      </c>
-      <c r="B23" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="C23" s="57">
+      <c r="A23" s="57" t="str">
+        <v>W04</v>
+      </c>
+      <c r="B23" s="57" t="str">
+        <v>W04-P01</v>
+      </c>
+      <c r="C23" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E23" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="F23" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="56">
+      <c r="D23" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E23" s="57" t="str">
+        <v>FromAnnualMainVacation</v>
+      </c>
+      <c r="F23" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G23" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H23" s="57" t="s">
-        <v>86</v>
+      <c r="H23" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I23" s="57"/>
       <c r="J23" s="57"/>
-      <c r="K23" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L23" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M23" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N23" s="57" t="s">
-        <v>134</v>
+      <c r="K23" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L23" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M23" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N23" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O23" s="57"/>
       <c r="P23" s="57"/>
       <c r="Q23" s="57"/>
-      <c r="R23" s="57" t="s">
-        <v>295</v>
-      </c>
-      <c r="S23" s="56">
+      <c r="R23" s="57" t="str">
+        <v>1656/1255-в (ТЕСТ-W04)</v>
+      </c>
+      <c r="S23" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T23" s="57"/>
       <c r="U23" s="56"/>
       <c r="V23" s="57"/>
-      <c r="W23" s="56">
+      <c r="W23" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X23" s="57" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y23" s="56">
+      <c r="X23" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-W04)</v>
+      </c>
+      <c r="Y23" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z23" s="57"/>
     </row>
     <row r="24" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="57" t="s">
-        <v>257</v>
-      </c>
-      <c r="B24" s="57" t="s">
-        <v>296</v>
-      </c>
-      <c r="C24" s="57">
+      <c r="A24" s="57" t="str">
+        <v>W05</v>
+      </c>
+      <c r="B24" s="57" t="str">
+        <v>W05-P01</v>
+      </c>
+      <c r="C24" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E24" s="57" t="s">
-        <v>340</v>
-      </c>
-      <c r="F24" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G24" s="56">
+      <c r="D24" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E24" s="57" t="str">
+        <v>ToVacationForCuring</v>
+      </c>
+      <c r="F24" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G24" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H24" s="57" t="s">
-        <v>86</v>
+      <c r="H24" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I24" s="57"/>
       <c r="J24" s="57"/>
-      <c r="K24" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L24" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M24" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N24" s="57" t="s">
-        <v>134</v>
+      <c r="K24" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L24" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M24" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N24" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O24" s="57"/>
       <c r="P24" s="57"/>
       <c r="Q24" s="57"/>
-      <c r="R24" s="57" t="s">
-        <v>297</v>
-      </c>
-      <c r="S24" s="56">
+      <c r="R24" s="57" t="str">
+        <v>1656/1256-в (ТЕСТ-W05)</v>
+      </c>
+      <c r="S24" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T24" s="57"/>
       <c r="U24" s="56"/>
       <c r="V24" s="57"/>
-      <c r="W24" s="56">
+      <c r="W24" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X24" s="57" t="s">
-        <v>297</v>
-      </c>
-      <c r="Y24" s="56">
+      <c r="X24" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-W05)</v>
+      </c>
+      <c r="Y24" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z24" s="57"/>
     </row>
     <row r="25" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="B25" s="57" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="57">
+      <c r="A25" s="57" t="str">
+        <v>W06</v>
+      </c>
+      <c r="B25" s="57" t="str">
+        <v>W06-P01</v>
+      </c>
+      <c r="C25" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="F25" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="56">
+      <c r="D25" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E25" s="57" t="str">
+        <v>FromVacationForCuring</v>
+      </c>
+      <c r="F25" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G25" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H25" s="57" t="s">
-        <v>86</v>
+      <c r="H25" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I25" s="57"/>
       <c r="J25" s="57"/>
-      <c r="K25" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L25" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M25" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N25" s="57" t="s">
-        <v>134</v>
+      <c r="K25" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L25" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M25" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N25" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O25" s="57"/>
       <c r="P25" s="57"/>
       <c r="Q25" s="57"/>
-      <c r="R25" s="57" t="s">
-        <v>299</v>
-      </c>
-      <c r="S25" s="56">
+      <c r="R25" s="57" t="str">
+        <v>1656/1257-в (ТЕСТ-W06)</v>
+      </c>
+      <c r="S25" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T25" s="57"/>
       <c r="U25" s="56"/>
       <c r="V25" s="57"/>
-      <c r="W25" s="56">
+      <c r="W25" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X25" s="57" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y25" s="56">
+      <c r="X25" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-W06)</v>
+      </c>
+      <c r="Y25" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z25" s="57"/>
     </row>
     <row r="26" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="57" t="s">
-        <v>261</v>
-      </c>
-      <c r="B26" s="57" t="s">
-        <v>300</v>
-      </c>
-      <c r="C26" s="57">
+      <c r="A26" s="57" t="str">
+        <v>W07</v>
+      </c>
+      <c r="B26" s="57" t="str">
+        <v>W07-P01</v>
+      </c>
+      <c r="C26" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E26" s="57" t="s">
-        <v>341</v>
-      </c>
-      <c r="F26" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G26" s="56">
+      <c r="D26" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E26" s="57" t="str">
+        <v>ToVacationForFamily</v>
+      </c>
+      <c r="F26" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G26" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H26" s="57" t="s">
-        <v>86</v>
+      <c r="H26" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I26" s="57"/>
       <c r="J26" s="57"/>
-      <c r="K26" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L26" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M26" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N26" s="57" t="s">
-        <v>134</v>
+      <c r="K26" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L26" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M26" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N26" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O26" s="57"/>
       <c r="P26" s="57"/>
       <c r="Q26" s="57"/>
-      <c r="R26" s="57" t="s">
-        <v>301</v>
-      </c>
-      <c r="S26" s="56">
+      <c r="R26" s="57" t="str">
+        <v>1656/1258-в (ТЕСТ-W07)</v>
+      </c>
+      <c r="S26" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T26" s="57"/>
       <c r="U26" s="56"/>
       <c r="V26" s="57"/>
-      <c r="W26" s="56">
+      <c r="W26" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X26" s="57" t="s">
-        <v>301</v>
-      </c>
-      <c r="Y26" s="56">
+      <c r="X26" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-W07)</v>
+      </c>
+      <c r="Y26" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z26" s="57"/>
     </row>
     <row r="27" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="57" t="s">
-        <v>263</v>
-      </c>
-      <c r="B27" s="57" t="s">
-        <v>302</v>
-      </c>
-      <c r="C27" s="57">
+      <c r="A27" s="57" t="str">
+        <v>W08</v>
+      </c>
+      <c r="B27" s="57" t="str">
+        <v>W08-P01</v>
+      </c>
+      <c r="C27" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E27" s="57" t="s">
-        <v>345</v>
-      </c>
-      <c r="F27" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G27" s="56">
+      <c r="D27" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E27" s="57" t="str">
+        <v>FromVacationForFamily</v>
+      </c>
+      <c r="F27" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G27" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="H27" s="57" t="s">
-        <v>86</v>
+      <c r="H27" s="57" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I27" s="57"/>
       <c r="J27" s="57"/>
-      <c r="K27" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L27" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M27" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N27" s="57" t="s">
-        <v>134</v>
+      <c r="K27" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L27" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M27" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N27" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O27" s="57"/>
       <c r="P27" s="57"/>
       <c r="Q27" s="57"/>
-      <c r="R27" s="57" t="s">
-        <v>303</v>
-      </c>
-      <c r="S27" s="56">
+      <c r="R27" s="57" t="str">
+        <v>1656/1259-в (ТЕСТ-W08)</v>
+      </c>
+      <c r="S27" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T27" s="57"/>
       <c r="U27" s="56"/>
       <c r="V27" s="57"/>
-      <c r="W27" s="56">
+      <c r="W27" s="56" t="n">
         <v>46310</v>
       </c>
-      <c r="X27" s="57" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y27" s="56">
+      <c r="X27" s="57" t="str">
+        <v>2026/115/7 (ТЕСТ-W08)</v>
+      </c>
+      <c r="Y27" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="Z27" s="57"/>
     </row>
     <row r="28" spans="1:26" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="57" t="s">
-        <v>265</v>
-      </c>
-      <c r="B28" s="57" t="s">
-        <v>304</v>
-      </c>
-      <c r="C28" s="57">
+      <c r="A28" s="57" t="str">
+        <v>W09</v>
+      </c>
+      <c r="B28" s="57" t="str">
+        <v>W09-P01</v>
+      </c>
+      <c r="C28" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="E28" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="F28" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="56">
+      <c r="D28" s="57" t="str">
+        <v>PreviewWord</v>
+      </c>
+      <c r="E28" s="57" t="str">
+        <v>ToHospital</v>
+      </c>
+      <c r="F28" s="57" t="str">
+        <v>115</v>
+      </c>
+      <c r="G28" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="H28" s="57"/>
       <c r="I28" s="57"/>
-      <c r="J28" s="57" t="s">
-        <v>111</v>
-      </c>
-      <c r="K28" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="L28" s="57" t="s">
-        <v>15</v>
-      </c>
-      <c r="M28" s="57" t="s">
-        <v>133</v>
-      </c>
-      <c r="N28" s="57" t="s">
-        <v>134</v>
+      <c r="J28" s="57" t="str">
+        <v>ТЕСТ-ЛЗ-01</v>
+      </c>
+      <c r="K28" s="57" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="L28" s="57" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="M28" s="57" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="N28" s="57" t="str">
+        <v>В00К3252</v>
       </c>
       <c r="O28" s="57"/>
       <c r="P28" s="57"/>
       <c r="Q28" s="57"/>
-      <c r="R28" s="57" t="s">
-        <v>305</v>
-      </c>
-      <c r="S28" s="56">
+      <c r="R28" s="57" t="str">
+        <v>1656/1260-в (ТЕСТ-W09)</v>
+      </c>
+      <c r="S28" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="T28" s="57"/>
       <c r="U28" s="56"/>
       <c r="V28" s="57"/>
-      <c r="W28" s="56">
+      <c r="W28" s="56" t="n">
         <v>46310</v>
       </c>
       <c r="X28" s="57"/>
@@ -37269,457 +37285,687 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="E1" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>355</v>
+      <c r="A1" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StepId</t>
+        </is>
+      </c>
+      <c r="B1" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExpectedDecision</t>
+        </is>
+      </c>
+      <c r="C1" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExpectedCode</t>
+        </is>
+      </c>
+      <c r="D1" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StateCheck</t>
+        </is>
+      </c>
+      <c r="E1" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExpectedOpenCount</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подія</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">За межі</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Опис</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
-        <v>269</v>
-      </c>
-      <c r="B2" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" s="47" t="s">
-        <v>307</v>
+      <c r="A2" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S01-M01</t>
+        </is>
+      </c>
+      <c r="B2" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C2" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NoOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D2" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E2" s="47">
         <v>1</v>
       </c>
-      <c r="H2" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="70" t="s">
-        <v>354</v>
+      <c r="H2" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Щорічна відпустка</t>
+        </is>
+      </c>
+      <c r="I2" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J2" s="71"/>
     </row>
     <row r="3" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>307</v>
+      <c r="A3" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S05-M01</t>
+        </is>
+      </c>
+      <c r="B3" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C3" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MatchingOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D3" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E3" s="47">
         <v>0</v>
       </c>
-      <c r="H3" s="69" t="s">
-        <v>356</v>
-      </c>
-      <c r="I3" s="70" t="s">
-        <v>354</v>
+      <c r="H3" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Відпочинок за донацію крові</t>
+        </is>
+      </c>
+      <c r="I3" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J3" s="71"/>
     </row>
     <row r="4" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>307</v>
+      <c r="A4" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S02-M01</t>
+        </is>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NoOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E4" s="47">
         <v>1</v>
       </c>
-      <c r="H4" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="70" t="s">
-        <v>354</v>
+      <c r="H4" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Відпустка за сімейними обставинами</t>
+        </is>
+      </c>
+      <c r="I4" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J4" s="71"/>
     </row>
     <row r="5" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
-        <v>273</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>307</v>
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S06-M01</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C5" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MatchingOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D5" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E5" s="47">
         <v>0</v>
       </c>
-      <c r="H5" s="69" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="70" t="s">
-        <v>354</v>
+      <c r="H5" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Відпустка для лікування</t>
+        </is>
+      </c>
+      <c r="I5" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J5" s="71"/>
     </row>
     <row r="6" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>307</v>
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S03-M01</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NoOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D6" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E6" s="47">
         <v>1</v>
       </c>
-      <c r="H6" s="69" t="s">
-        <v>357</v>
-      </c>
-      <c r="I6" s="70" t="s">
-        <v>354</v>
+      <c r="H6" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Відпустка у зв'язку з вагітністю та пологами</t>
+        </is>
+      </c>
+      <c r="I6" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J6" s="71"/>
     </row>
     <row r="7" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>307</v>
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S07-M01</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MatchingOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E7" s="47">
         <v>0</v>
       </c>
-      <c r="H7" s="69" t="s">
-        <v>358</v>
-      </c>
-      <c r="I7" s="70" t="s">
-        <v>354</v>
+      <c r="H7" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Відпустка по догляду за дитиною</t>
+        </is>
+      </c>
+      <c r="I7" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J7" s="71"/>
     </row>
     <row r="8" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>307</v>
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S04-M01</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NoOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E8" s="47">
         <v>1</v>
       </c>
-      <c r="H8" s="69" t="s">
-        <v>359</v>
-      </c>
-      <c r="I8" s="70" t="s">
-        <v>354</v>
+      <c r="H8" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Відрядження</t>
+        </is>
+      </c>
+      <c r="I8" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J8" s="71"/>
     </row>
     <row r="9" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>307</v>
+      <c r="A9" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S08-M01</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MatchingOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E9" s="47">
         <v>0</v>
       </c>
-      <c r="H9" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="70" t="s">
-        <v>354</v>
+      <c r="H9" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Стаціонарне лікування</t>
+        </is>
+      </c>
+      <c r="I9" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J9" s="71"/>
     </row>
     <row r="10" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
-        <v>278</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>308</v>
+      <c r="A10" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S09-M01</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Block</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenDepartureExists</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unchanged</t>
+        </is>
       </c>
       <c r="E10" s="47">
         <v>1</v>
       </c>
-      <c r="H10" s="69" t="s">
-        <v>360</v>
-      </c>
-      <c r="I10" s="70" t="s">
-        <v>354</v>
+      <c r="H10" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Самовільне залишення частини</t>
+        </is>
+      </c>
+      <c r="I10" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J10" s="71"/>
     </row>
     <row r="11" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>307</v>
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S10-M01</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PreviousDepartureClosed</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E11" s="47">
         <v>1</v>
       </c>
-      <c r="H11" s="69" t="s">
-        <v>361</v>
-      </c>
-      <c r="I11" s="70" t="s">
-        <v>354</v>
+      <c r="H11" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Повернення до іншої частини</t>
+        </is>
+      </c>
+      <c r="I11" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J11" s="71"/>
     </row>
     <row r="12" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="47" t="s">
-        <v>280</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>308</v>
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S11-M01</t>
+        </is>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Block</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AmbiguousOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unchanged</t>
+        </is>
       </c>
       <c r="E12" s="47">
         <v>2</v>
       </c>
-      <c r="H12" s="69" t="s">
-        <v>362</v>
-      </c>
-      <c r="I12" s="70" t="s">
-        <v>354</v>
+      <c r="H12" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Полон</t>
+        </is>
+      </c>
+      <c r="I12" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J12" s="71"/>
     </row>
     <row r="13" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
-        <v>281</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>308</v>
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S12-M01</t>
+        </is>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Block</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenDepartureNotFound</t>
+        </is>
+      </c>
+      <c r="D13" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unchanged</t>
+        </is>
       </c>
       <c r="E13" s="47">
         <v>0</v>
       </c>
-      <c r="H13" s="69" t="s">
-        <v>363</v>
-      </c>
-      <c r="I13" s="70" t="s">
-        <v>354</v>
+      <c r="H13" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Безвісти зниклий</t>
+        </is>
+      </c>
+      <c r="I13" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J13" s="71"/>
     </row>
     <row r="14" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>308</v>
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S13-M01</t>
+        </is>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Block</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ArrivalBeforeDeparture</t>
+        </is>
+      </c>
+      <c r="D14" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unchanged</t>
+        </is>
       </c>
       <c r="E14" s="47">
         <v>1</v>
       </c>
-      <c r="H14" s="69" t="s">
-        <v>364</v>
-      </c>
-      <c r="I14" s="70" t="s">
-        <v>354</v>
+      <c r="H14" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Арешт</t>
+        </is>
+      </c>
+      <c r="I14" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J14" s="71"/>
     </row>
     <row r="15" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>308</v>
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S14-M01</t>
+        </is>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NoChange</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuplicateEvent</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unchanged</t>
+        </is>
       </c>
       <c r="E15" s="47">
         <v>1</v>
       </c>
-      <c r="H15" s="69" t="s">
-        <v>365</v>
-      </c>
-      <c r="I15" s="70" t="s">
-        <v>9</v>
+      <c r="H15" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Звільнення від виконання службових обов'язків</t>
+        </is>
+      </c>
+      <c r="I15" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ні</t>
+        </is>
       </c>
       <c r="J15" s="71"/>
     </row>
     <row r="16" spans="1:10" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>130</v>
+      <c r="A16" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S15-M01</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExceptionRuleNotDefined</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pending</t>
+        </is>
       </c>
       <c r="E16" s="47"/>
-      <c r="H16" s="69" t="s">
-        <v>366</v>
-      </c>
-      <c r="I16" s="70" t="s">
-        <v>9</v>
+      <c r="H16" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Амбулаторне лікування</t>
+        </is>
+      </c>
+      <c r="I16" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ні</t>
+        </is>
       </c>
       <c r="J16" s="71"/>
     </row>
     <row r="17" spans="1:25" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>307</v>
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S16-M01</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NoOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E17" s="47">
         <v>1</v>
       </c>
-      <c r="H17" s="69" t="s">
-        <v>367</v>
-      </c>
-      <c r="I17" s="70" t="s">
-        <v>9</v>
+      <c r="H17" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Амбулаторне ВЛК</t>
+        </is>
+      </c>
+      <c r="I17" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ні</t>
+        </is>
       </c>
       <c r="J17" s="71"/>
     </row>
     <row r="18" spans="1:25" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>307</v>
+      <c r="A18" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S16-M02</t>
+        </is>
+      </c>
+      <c r="B18" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MatchingOpenDeparture</t>
+        </is>
+      </c>
+      <c r="D18" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E18" s="47">
         <v>0</v>
       </c>
-      <c r="H18" s="69" t="s">
-        <v>368</v>
-      </c>
-      <c r="I18" s="70" t="s">
-        <v>354</v>
+      <c r="H18" s="69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ВЛК за межами</t>
+        </is>
+      </c>
+      <c r="I18" s="70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Так</t>
+        </is>
       </c>
       <c r="J18" s="71"/>
     </row>
     <row r="19" spans="1:25" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>307</v>
+      <c r="A19" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S16-M03</t>
+        </is>
+      </c>
+      <c r="B19" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow</t>
+        </is>
+      </c>
+      <c r="C19" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PreviousDepartureClosed</t>
+        </is>
+      </c>
+      <c r="D19" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snapshot</t>
+        </is>
       </c>
       <c r="E19" s="47">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="45" t="s">
-        <v>309</v>
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Очікувані рядки після кроку</t>
+        </is>
       </c>
       <c r="B21" s="45"/>
       <c r="C21" s="45"/>
@@ -37728,125 +37974,124 @@
       <c r="F21" s="45"/>
     </row>
     <row r="23" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="68" t="s">
-        <v>8</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="K23" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="O23" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="P23" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R23" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="S23" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="T23" s="68" t="s">
-        <v>6</v>
-      </c>
-      <c r="U23" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="V23" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="W23" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="X23" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y23" s="46" t="s">
-        <v>7</v>
+      <c r="A23" s="46" t="str">
+        <v>StepId</v>
+      </c>
+      <c r="B23" s="46" t="str">
+        <v>RecordId</v>
+      </c>
+      <c r="C23" s="46" t="str">
+        <v>Звання</v>
+      </c>
+      <c r="D23" s="46" t="str">
+        <v>ПІБ</v>
+      </c>
+      <c r="E23" s="46" t="str">
+        <v>ІПН</v>
+      </c>
+      <c r="F23" s="46" t="str">
+        <v>Посада</v>
+      </c>
+      <c r="G23" s="68" t="str">
+        <v>Подія</v>
+      </c>
+      <c r="H23" s="48" t="str">
+        <v>Куди</v>
+      </c>
+      <c r="I23" s="68" t="str">
+        <v>За межі</v>
+      </c>
+      <c r="J23" s="46" t="str">
+        <v>Вибуття.Наказ</v>
+      </c>
+      <c r="K23" s="46" t="str">
+        <v>Вибуття.Продовольче</v>
+      </c>
+      <c r="L23" s="46" t="str">
+        <v>Вибуття</v>
+      </c>
+      <c r="M23" s="46" t="str">
+        <v>Вибуття.Термін</v>
+      </c>
+      <c r="N23" s="46" t="str">
+        <v>Вибуття.Дорога</v>
+      </c>
+      <c r="O23" s="46" t="str">
+        <v>Прибуття.План</v>
+      </c>
+      <c r="P23" s="46" t="str">
+        <v>Прибуття</v>
+      </c>
+      <c r="Q23" s="46" t="str">
+        <v>Прибуття.Продовольче</v>
+      </c>
+      <c r="R23" s="46" t="str">
+        <v>Прибуття.Наказ</v>
+      </c>
+      <c r="S23" s="68" t="str">
+        <v>Вибуття.Підстава</v>
+      </c>
+      <c r="T23" s="68" t="str">
+        <v>Супровідний документ</v>
+      </c>
+      <c r="U23" s="46" t="str">
+        <v>Прибуття.Підстава</v>
+      </c>
+      <c r="V23" s="46" t="str">
+        <v>ТВО.ПІБ</v>
+      </c>
+      <c r="W23" s="46" t="str">
+        <v>ТВО.ІПН</v>
+      </c>
+      <c r="X23" s="46" t="str">
+        <v>ТВО.Посада</v>
+      </c>
+      <c r="Y23" s="46" t="str">
+        <v>Додаткова інформація</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
-        <v>269</v>
-      </c>
-      <c r="B24" s="47" t="s">
-        <v>311</v>
+      <c r="A24" s="47" t="str">
+        <v>S01-M01</v>
+      </c>
+      <c r="B24" s="47" t="str">
+        <v>R01</v>
       </c>
       <c r="C24" s="47"/>
-      <c r="D24" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>133</v>
+      <c r="D24" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E24" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F24" s="47"/>
-      <c r="G24" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="50" t="s">
-        <v>335</v>
+      <c r="G24" s="49" t="str">
+        <v>Стаціонарне лікування</v>
+      </c>
+      <c r="H24" s="50" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
       </c>
       <c r="I24" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J24" s="47" t="s">
-        <v>97</v>
+      <c r="J24" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K24" s="47"/>
-      <c r="L24" s="52">
+      <c r="L24" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="M24" s="47"/>
       <c r="N24" s="47"/>
       <c r="O24" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
       </c>
       <c r="P24" s="52"/>
       <c r="Q24" s="47"/>
       <c r="R24" s="47"/>
-      <c r="S24" s="47" t="s">
-        <v>228</v>
+      <c r="S24" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1234-в (ТЕСТ-S01-1) від 15.10.2026).</v>
       </c>
       <c r="T24" s="47"/>
       <c r="U24" s="47"/>
@@ -37856,50 +38101,51 @@
       <c r="Y24" s="47"/>
     </row>
     <row r="25" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="47" t="s">
-        <v>272</v>
-      </c>
-      <c r="B25" s="47" t="s">
-        <v>311</v>
+      <c r="A25" s="47" t="str">
+        <v>S02-M01</v>
+      </c>
+      <c r="B25" s="47" t="str">
+        <v>R01</v>
       </c>
       <c r="C25" s="47"/>
-      <c r="D25" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>133</v>
+      <c r="D25" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E25" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F25" s="47"/>
-      <c r="G25" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="H25" s="50" t="s">
-        <v>86</v>
+      <c r="G25" s="49" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H25" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I25" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J25" s="47" t="s">
-        <v>97</v>
+      <c r="J25" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K25" s="47"/>
-      <c r="L25" s="52">
+      <c r="L25" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="M25" s="47"/>
       <c r="N25" s="47"/>
       <c r="O25" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
       </c>
       <c r="P25" s="52"/>
       <c r="Q25" s="47"/>
       <c r="R25" s="47"/>
-      <c r="S25" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="T25" s="47"/>
+      <c r="S25" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1235-в (ТЕСТ-S02-1) від 15.10.2026).</v>
+      </c>
+      <c r="T25" s="47" t="str">
+        <v>2026/115/7 (ТЕСТ-S02-1)</v>
+      </c>
       <c r="U25" s="47"/>
       <c r="V25" s="47"/>
       <c r="W25" s="47"/>
@@ -37907,50 +38153,51 @@
       <c r="Y25" s="47"/>
     </row>
     <row r="26" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
-        <v>274</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>311</v>
+      <c r="A26" s="47" t="str">
+        <v>S03-M01</v>
+      </c>
+      <c r="B26" s="47" t="str">
+        <v>R01</v>
       </c>
       <c r="C26" s="47"/>
-      <c r="D26" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>133</v>
+      <c r="D26" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E26" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F26" s="47"/>
-      <c r="G26" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="50" t="s">
-        <v>86</v>
+      <c r="G26" s="49" t="str">
+        <v>Відпустка для лікування</v>
+      </c>
+      <c r="H26" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I26" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J26" s="47" t="s">
-        <v>97</v>
+      <c r="J26" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K26" s="47"/>
-      <c r="L26" s="52">
+      <c r="L26" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="M26" s="47"/>
       <c r="N26" s="47"/>
       <c r="O26" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
       </c>
       <c r="P26" s="52"/>
       <c r="Q26" s="47"/>
       <c r="R26" s="47"/>
-      <c r="S26" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="T26" s="47"/>
+      <c r="S26" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1236-в (ТЕСТ-S03-1) від 15.10.2026).</v>
+      </c>
+      <c r="T26" s="47" t="str">
+        <v>2026/115/7 (ТЕСТ-S03-1)</v>
+      </c>
       <c r="U26" s="47"/>
       <c r="V26" s="47"/>
       <c r="W26" s="47"/>
@@ -37958,50 +38205,51 @@
       <c r="Y26" s="47"/>
     </row>
     <row r="27" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="B27" s="47" t="s">
-        <v>311</v>
+      <c r="A27" s="47" t="str">
+        <v>S04-M01</v>
+      </c>
+      <c r="B27" s="47" t="str">
+        <v>R01</v>
       </c>
       <c r="C27" s="47"/>
-      <c r="D27" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>133</v>
+      <c r="D27" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E27" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F27" s="47"/>
-      <c r="G27" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="50" t="s">
-        <v>86</v>
+      <c r="G27" s="49" t="str">
+        <v>Відпустка за сімейними обставинами</v>
+      </c>
+      <c r="H27" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I27" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J27" s="47" t="s">
-        <v>97</v>
+      <c r="J27" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K27" s="47"/>
-      <c r="L27" s="52">
+      <c r="L27" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="M27" s="47"/>
       <c r="N27" s="47"/>
       <c r="O27" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
       </c>
       <c r="P27" s="52"/>
       <c r="Q27" s="47"/>
       <c r="R27" s="47"/>
-      <c r="S27" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="T27" s="47"/>
+      <c r="S27" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1237-в (ТЕСТ-S04-1) від 15.10.2026).</v>
+      </c>
+      <c r="T27" s="47" t="str">
+        <v>2026/115/7 (ТЕСТ-S04-1)</v>
+      </c>
       <c r="U27" s="47"/>
       <c r="V27" s="47"/>
       <c r="W27" s="47"/>
@@ -38009,373 +38257,380 @@
       <c r="Y27" s="47"/>
     </row>
     <row r="28" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="B28" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="50" t="s">
-        <v>335</v>
+      <c r="A28" s="47" t="str">
+        <v>S05-M01</v>
+      </c>
+      <c r="B28" s="47" t="str">
+        <v>R01</v>
+      </c>
+      <c r="C28" s="47" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D28" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E28" s="47" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F28" s="47" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G28" s="49" t="str">
+        <v>Стаціонарне лікування</v>
+      </c>
+      <c r="H28" s="50" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
       </c>
       <c r="I28" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J28" s="47" t="s">
-        <v>83</v>
+      <c r="J28" s="47" t="str">
+        <v>100</v>
       </c>
       <c r="K28" s="47"/>
-      <c r="L28" s="52">
+      <c r="L28" s="52" t="n">
         <v>46296</v>
       </c>
-      <c r="M28" s="47">
+      <c r="M28" s="47" t="n">
         <v>10</v>
       </c>
       <c r="N28" s="47"/>
-      <c r="O28" s="53">
+      <c r="O28" s="53" t="n">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
         <v>46306</v>
       </c>
-      <c r="P28" s="52">
+      <c r="P28" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="Q28" s="47"/>
-      <c r="R28" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="S28" s="47" t="s">
-        <v>84</v>
+      <c r="R28" s="47" t="str">
+        <v>115</v>
+      </c>
+      <c r="S28" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1200-в (ТЕСТ-S05-H01) від 01.10.2026).</v>
       </c>
       <c r="T28" s="47"/>
-      <c r="U28" s="47" t="s">
-        <v>229</v>
+      <c r="U28" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1238-в (ТЕСТ-S05-1) від 15.10.2026).</v>
       </c>
       <c r="V28" s="47"/>
       <c r="W28" s="47"/>
       <c r="X28" s="47"/>
-      <c r="Y28" s="47" t="s">
-        <v>85</v>
+      <c r="Y28" s="47" t="str">
+        <v>Fixture S05</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="47" t="s">
-        <v>273</v>
-      </c>
-      <c r="B29" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="G29" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="50" t="s">
-        <v>86</v>
+      <c r="A29" s="47" t="str">
+        <v>S06-M01</v>
+      </c>
+      <c r="B29" s="47" t="str">
+        <v>R01</v>
+      </c>
+      <c r="C29" s="47" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D29" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E29" s="47" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F29" s="47" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G29" s="49" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H29" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I29" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J29" s="47" t="s">
-        <v>83</v>
+      <c r="J29" s="47" t="str">
+        <v>100</v>
       </c>
       <c r="K29" s="47"/>
-      <c r="L29" s="52">
+      <c r="L29" s="52" t="n">
         <v>46296</v>
       </c>
-      <c r="M29" s="47">
+      <c r="M29" s="47" t="n">
         <v>10</v>
       </c>
       <c r="N29" s="47"/>
-      <c r="O29" s="53">
+      <c r="O29" s="53" t="n">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
         <v>46306</v>
       </c>
-      <c r="P29" s="52">
+      <c r="P29" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="Q29" s="47"/>
-      <c r="R29" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="S29" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="T29" s="47"/>
-      <c r="U29" s="47" t="s">
-        <v>231</v>
+      <c r="R29" s="47" t="str">
+        <v>115</v>
+      </c>
+      <c r="S29" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1201-в (ТЕСТ-S06-H02) від 01.10.2026).</v>
+      </c>
+      <c r="T29" s="47" t="str">
+        <v>2026/100/7 (ТЕСТ-S06-H02)</v>
+      </c>
+      <c r="U29" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1239-в (ТЕСТ-S06-1) від 15.10.2026).</v>
       </c>
       <c r="V29" s="47"/>
       <c r="W29" s="47"/>
       <c r="X29" s="47"/>
-      <c r="Y29" s="47" t="s">
-        <v>87</v>
+      <c r="Y29" s="47" t="str">
+        <v>Fixture S06</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="B30" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="C30" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="F30" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="G30" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="50" t="s">
-        <v>86</v>
+      <c r="A30" s="47" t="str">
+        <v>S07-M01</v>
+      </c>
+      <c r="B30" s="47" t="str">
+        <v>R01</v>
+      </c>
+      <c r="C30" s="47" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D30" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E30" s="47" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F30" s="47" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G30" s="49" t="str">
+        <v>Відпустка для лікування</v>
+      </c>
+      <c r="H30" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I30" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J30" s="47" t="s">
-        <v>83</v>
+      <c r="J30" s="47" t="str">
+        <v>100</v>
       </c>
       <c r="K30" s="47"/>
-      <c r="L30" s="52">
+      <c r="L30" s="52" t="n">
         <v>46296</v>
       </c>
-      <c r="M30" s="47">
+      <c r="M30" s="47" t="n">
         <v>10</v>
       </c>
       <c r="N30" s="47"/>
-      <c r="O30" s="53">
+      <c r="O30" s="53" t="n">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
         <v>46306</v>
       </c>
-      <c r="P30" s="52">
+      <c r="P30" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="Q30" s="47"/>
-      <c r="R30" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="S30" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="T30" s="47"/>
-      <c r="U30" s="47" t="s">
-        <v>233</v>
+      <c r="R30" s="47" t="str">
+        <v>115</v>
+      </c>
+      <c r="S30" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1202-в (ТЕСТ-S07-H03) від 01.10.2026).</v>
+      </c>
+      <c r="T30" s="47" t="str">
+        <v>2026/100/7 (ТЕСТ-S07-H03)</v>
+      </c>
+      <c r="U30" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1240-в (ТЕСТ-S07-1) від 15.10.2026).</v>
       </c>
       <c r="V30" s="47"/>
       <c r="W30" s="47"/>
       <c r="X30" s="47"/>
-      <c r="Y30" s="47" t="s">
-        <v>88</v>
+      <c r="Y30" s="47" t="str">
+        <v>Fixture S07</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="B31" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="F31" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="G31" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>86</v>
+      <c r="A31" s="47" t="str">
+        <v>S08-M01</v>
+      </c>
+      <c r="B31" s="47" t="str">
+        <v>R01</v>
+      </c>
+      <c r="C31" s="47" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D31" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E31" s="47" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F31" s="47" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G31" s="49" t="str">
+        <v>Відпустка за сімейними обставинами</v>
+      </c>
+      <c r="H31" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I31" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J31" s="47" t="s">
-        <v>83</v>
+      <c r="J31" s="47" t="str">
+        <v>100</v>
       </c>
       <c r="K31" s="47"/>
-      <c r="L31" s="52">
+      <c r="L31" s="52" t="n">
         <v>46296</v>
       </c>
-      <c r="M31" s="47">
+      <c r="M31" s="47" t="n">
         <v>10</v>
       </c>
       <c r="N31" s="47"/>
-      <c r="O31" s="53">
+      <c r="O31" s="53" t="n">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
         <v>46306</v>
       </c>
-      <c r="P31" s="52">
+      <c r="P31" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="Q31" s="47"/>
-      <c r="R31" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="S31" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="T31" s="47"/>
-      <c r="U31" s="47" t="s">
-        <v>235</v>
+      <c r="R31" s="47" t="str">
+        <v>115</v>
+      </c>
+      <c r="S31" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1203-в (ТЕСТ-S08-H04) від 01.10.2026).</v>
+      </c>
+      <c r="T31" s="47" t="str">
+        <v>2026/100/7 (ТЕСТ-S08-H04)</v>
+      </c>
+      <c r="U31" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1241-в (ТЕСТ-S08-1) від 15.10.2026).</v>
       </c>
       <c r="V31" s="47"/>
       <c r="W31" s="47"/>
       <c r="X31" s="47"/>
-      <c r="Y31" s="47" t="s">
-        <v>89</v>
+      <c r="Y31" s="47" t="str">
+        <v>Fixture S08</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="B32" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="F32" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="H32" s="50" t="s">
-        <v>86</v>
+      <c r="A32" s="47" t="str">
+        <v>S10-M01</v>
+      </c>
+      <c r="B32" s="47" t="str">
+        <v>R01</v>
+      </c>
+      <c r="C32" s="47" t="str">
+        <v>лейтенант</v>
+      </c>
+      <c r="D32" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E32" s="47" t="str">
+        <v>ipn_0001</v>
+      </c>
+      <c r="F32" s="47" t="str">
+        <v>В00К3252</v>
+      </c>
+      <c r="G32" s="49" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H32" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I32" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J32" s="47" t="s">
-        <v>83</v>
+      <c r="J32" s="47" t="str">
+        <v>100</v>
       </c>
       <c r="K32" s="47"/>
-      <c r="L32" s="52">
+      <c r="L32" s="52" t="n">
         <v>46266</v>
       </c>
-      <c r="M32" s="47">
+      <c r="M32" s="47" t="n">
         <v>10</v>
       </c>
       <c r="N32" s="47"/>
-      <c r="O32" s="53">
+      <c r="O32" s="53" t="n">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
         <v>46276</v>
       </c>
-      <c r="P32" s="52">
+      <c r="P32" s="52" t="n">
         <v>46275</v>
       </c>
       <c r="Q32" s="47"/>
-      <c r="R32" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="S32" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="T32" s="47"/>
-      <c r="U32" s="47" t="s">
-        <v>92</v>
+      <c r="R32" s="47" t="str">
+        <v>110</v>
+      </c>
+      <c r="S32" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1205-в (ТЕСТ-S10-H06) від 01.09.2026).</v>
+      </c>
+      <c r="T32" s="47" t="str">
+        <v>2026/100/7 (ТЕСТ-S10-H06)</v>
+      </c>
+      <c r="U32" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1305-в (ТЕСТ-S10-H06-A) від 10.09.2026).</v>
       </c>
       <c r="V32" s="47"/>
       <c r="W32" s="47"/>
       <c r="X32" s="47"/>
-      <c r="Y32" s="47" t="s">
-        <v>93</v>
+      <c r="Y32" s="47" t="str">
+        <v>Fixture S10</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="B33" s="47" t="s">
-        <v>312</v>
+      <c r="A33" s="47" t="str">
+        <v>S10-M01</v>
+      </c>
+      <c r="B33" s="47" t="str">
+        <v>R02</v>
       </c>
       <c r="C33" s="47"/>
-      <c r="D33" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="47" t="s">
-        <v>133</v>
+      <c r="D33" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E33" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F33" s="47"/>
-      <c r="G33" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33" s="50" t="s">
-        <v>335</v>
+      <c r="G33" s="49" t="str">
+        <v>Стаціонарне лікування</v>
+      </c>
+      <c r="H33" s="50" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
       </c>
       <c r="I33" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J33" s="47" t="s">
-        <v>97</v>
+      <c r="J33" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K33" s="47"/>
-      <c r="L33" s="52">
+      <c r="L33" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="M33" s="47"/>
       <c r="N33" s="47"/>
       <c r="O33" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
       </c>
       <c r="P33" s="52"/>
       <c r="Q33" s="47"/>
       <c r="R33" s="47"/>
-      <c r="S33" s="47" t="s">
-        <v>237</v>
+      <c r="S33" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1243-в (ТЕСТ-S10-1) від 15.10.2026).</v>
       </c>
       <c r="T33" s="47"/>
       <c r="U33" s="47"/>
@@ -38385,50 +38640,51 @@
       <c r="Y33" s="47"/>
     </row>
     <row r="34" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="B34" s="47" t="s">
-        <v>311</v>
+      <c r="A34" s="47" t="str">
+        <v>S16-M01</v>
+      </c>
+      <c r="B34" s="47" t="str">
+        <v>R01</v>
       </c>
       <c r="C34" s="47"/>
-      <c r="D34" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>133</v>
+      <c r="D34" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E34" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F34" s="47"/>
-      <c r="G34" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="H34" s="50" t="s">
-        <v>86</v>
+      <c r="G34" s="49" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H34" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I34" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J34" s="47" t="s">
-        <v>97</v>
+      <c r="J34" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K34" s="47"/>
-      <c r="L34" s="52">
+      <c r="L34" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="M34" s="47"/>
       <c r="N34" s="47"/>
       <c r="O34" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
       </c>
       <c r="P34" s="52"/>
       <c r="Q34" s="47"/>
       <c r="R34" s="47"/>
-      <c r="S34" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="T34" s="47"/>
+      <c r="S34" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1249-в (ТЕСТ-S16-1) від 15.10.2026).</v>
+      </c>
+      <c r="T34" s="47" t="str">
+        <v>2026/115/7 (ТЕСТ-S16-1)</v>
+      </c>
       <c r="U34" s="47"/>
       <c r="V34" s="47"/>
       <c r="W34" s="47"/>
@@ -38436,56 +38692,57 @@
       <c r="Y34" s="47"/>
     </row>
     <row r="35" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="B35" s="47" t="s">
-        <v>311</v>
+      <c r="A35" s="47" t="str">
+        <v>S16-M02</v>
+      </c>
+      <c r="B35" s="47" t="str">
+        <v>R01</v>
       </c>
       <c r="C35" s="47"/>
-      <c r="D35" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="47" t="s">
-        <v>133</v>
+      <c r="D35" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E35" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F35" s="47"/>
-      <c r="G35" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="H35" s="50" t="s">
-        <v>86</v>
+      <c r="G35" s="49" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H35" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I35" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J35" s="47" t="s">
-        <v>97</v>
+      <c r="J35" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K35" s="47"/>
-      <c r="L35" s="52">
+      <c r="L35" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="M35" s="47"/>
       <c r="N35" s="47"/>
       <c r="O35" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
-      </c>
-      <c r="P35" s="52">
+      </c>
+      <c r="P35" s="52" t="n">
         <v>46315</v>
       </c>
       <c r="Q35" s="47"/>
-      <c r="R35" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="S35" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="T35" s="47"/>
-      <c r="U35" s="47" t="s">
-        <v>244</v>
+      <c r="R35" s="47" t="str">
+        <v>115</v>
+      </c>
+      <c r="S35" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1249-в (ТЕСТ-S16-1) від 15.10.2026).</v>
+      </c>
+      <c r="T35" s="47" t="str">
+        <v>2026/115/7 (ТЕСТ-S16-1)</v>
+      </c>
+      <c r="U35" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1250-в (ТЕСТ-S16-2) від 20.10.2026).</v>
       </c>
       <c r="V35" s="47"/>
       <c r="W35" s="47"/>
@@ -38493,56 +38750,57 @@
       <c r="Y35" s="47"/>
     </row>
     <row r="36" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="B36" s="47" t="s">
-        <v>311</v>
+      <c r="A36" s="47" t="str">
+        <v>S16-M03</v>
+      </c>
+      <c r="B36" s="47" t="str">
+        <v>R01</v>
       </c>
       <c r="C36" s="47"/>
-      <c r="D36" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="47" t="s">
-        <v>133</v>
+      <c r="D36" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E36" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F36" s="47"/>
-      <c r="G36" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="H36" s="50" t="s">
-        <v>86</v>
+      <c r="G36" s="49" t="str">
+        <v>Щорічна відпустка</v>
+      </c>
+      <c r="H36" s="50" t="str">
+        <v>м. Тестоград</v>
       </c>
       <c r="I36" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J36" s="47" t="s">
-        <v>97</v>
+      <c r="J36" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K36" s="47"/>
-      <c r="L36" s="52">
+      <c r="L36" s="52" t="n">
         <v>46310</v>
       </c>
       <c r="M36" s="47"/>
       <c r="N36" s="47"/>
       <c r="O36" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
-      </c>
-      <c r="P36" s="52">
+      </c>
+      <c r="P36" s="52" t="n">
         <v>46315</v>
       </c>
       <c r="Q36" s="47"/>
-      <c r="R36" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="S36" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="T36" s="47"/>
-      <c r="U36" s="47" t="s">
-        <v>244</v>
+      <c r="R36" s="47" t="str">
+        <v>115</v>
+      </c>
+      <c r="S36" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1249-в (ТЕСТ-S16-1) від 15.10.2026).</v>
+      </c>
+      <c r="T36" s="47" t="str">
+        <v>2026/115/7 (ТЕСТ-S16-1)</v>
+      </c>
+      <c r="U36" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1250-в (ТЕСТ-S16-2) від 20.10.2026).</v>
       </c>
       <c r="V36" s="47"/>
       <c r="W36" s="47"/>
@@ -38550,48 +38808,47 @@
       <c r="Y36" s="47"/>
     </row>
     <row r="37" spans="1:25" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="B37" s="47" t="s">
-        <v>312</v>
+      <c r="A37" s="47" t="str">
+        <v>S16-M03</v>
+      </c>
+      <c r="B37" s="47" t="str">
+        <v>R02</v>
       </c>
       <c r="C37" s="47"/>
-      <c r="D37" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="47" t="s">
-        <v>133</v>
+      <c r="D37" s="47" t="str">
+        <v>БОНДАРЕНКО Олександр Юрійович</v>
+      </c>
+      <c r="E37" s="47" t="str">
+        <v>ipn_0001</v>
       </c>
       <c r="F37" s="47"/>
-      <c r="G37" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="H37" s="50" t="s">
-        <v>335</v>
+      <c r="G37" s="49" t="str">
+        <v>Стаціонарне лікування</v>
+      </c>
+      <c r="H37" s="50" t="str">
+        <v>КНП МКБЛ №25 ХМР</v>
       </c>
       <c r="I37" s="51" t="str">
         <f>IF(tbExpectedMovementRows[[#This Row],[Подія]]="","",IF(AND(OR(tbExpectedMovementRows[[#This Row],[Подія]]="Стаціонарне лікування",tbExpectedMovementRows[[#This Row],[Подія]]="Відпустка для лікування"),tbExpectedMovementRows[[#This Row],[Куди]]="Медична рота А7383"),"Ні",_xlfn.XLOOKUP(tbExpectedMovementRows[[#This Row],[Подія]],tbMovementEnums[Подія],tbMovementEnums[За межі])))</f>
         <v>Так</v>
       </c>
-      <c r="J37" s="47" t="s">
-        <v>97</v>
+      <c r="J37" s="47" t="str">
+        <v>115</v>
       </c>
       <c r="K37" s="47"/>
-      <c r="L37" s="52">
+      <c r="L37" s="52" t="n">
         <v>46316</v>
       </c>
       <c r="M37" s="47"/>
       <c r="N37" s="47"/>
       <c r="O37" s="53" t="str">
         <f>IF(0&lt;LEN(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]]),tbExpectedMovementRows[[#This Row],[Вибуття]]+SUM(tbExpectedMovementRows[[#This Row],[Вибуття.Термін]],tbExpectedMovementRows[[#This Row],[Вибуття.Дорога]]),"")</f>
-        <v/>
       </c>
       <c r="P37" s="52"/>
       <c r="Q37" s="47"/>
       <c r="R37" s="47"/>
-      <c r="S37" s="47" t="s">
-        <v>245</v>
+      <c r="S37" s="47" t="str">
+        <v>рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1251-в (ТЕСТ-S16-3) від 21.10.2026).</v>
       </c>
       <c r="T37" s="47"/>
       <c r="U37" s="47"/>
@@ -38636,125 +38893,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>313</v>
-      </c>
-      <c r="C1" s="54" t="s">
-        <v>314</v>
-      </c>
-      <c r="D1" s="54" t="s">
-        <v>315</v>
+      <c r="A1" s="54" t="str">
+        <v>StepId</v>
+      </c>
+      <c r="B1" s="54" t="str">
+        <v>Outcome</v>
+      </c>
+      <c r="C1" s="54" t="str">
+        <v>ExpectedText</v>
+      </c>
+      <c r="D1" s="54" t="str">
+        <v>ExpectedError</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
-        <v>288</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>336</v>
+      <c r="A2" s="42" t="str">
+        <v>W01-P01</v>
+      </c>
+      <c r="B2" s="42" t="str">
+        <v>Success</v>
+      </c>
+      <c r="C2" s="43" t="str">
+        <v>У комунальне некомерційне підприємство "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради, з 15 жовтня 2026 року:
+лейтенанта БОНДАРЕНКА Олександра Юрійовича, ipn_0001, офіцера інформаційно-аналітичної групи штабу.
+Підстава: рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1252-в (ТЕСТ-W01) від 15.10.2026).</v>
       </c>
       <c r="D2" s="42"/>
     </row>
     <row r="3" spans="1:4" ht="126" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>337</v>
+      <c r="A3" s="42" t="str">
+        <v>W02-P01</v>
+      </c>
+      <c r="B3" s="42" t="str">
+        <v>Success</v>
+      </c>
+      <c r="C3" s="43" t="str">
+        <v>З 15 жовтня 2026 року:
+З комунального некомерційного підприємства "Міська клінічна багатопрофільна лікарня № 25" Харківської міської ради:
+лейтенанта БОНДАРЕНКА Олександра Юрійовича, ipn_0001, офіцера інформаційно-аналітичної групи штабу.
+Підстава: рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1253-в (ТЕСТ-W02) від 15.10.2026).</v>
       </c>
       <c r="D3" s="42"/>
     </row>
     <row r="4" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>317</v>
+      <c r="A4" s="42" t="str">
+        <v>W03-P01</v>
+      </c>
+      <c r="B4" s="42" t="str">
+        <v>Success</v>
+      </c>
+      <c r="C4" s="43" t="str">
+        <v>Лейтенанта БОНДАРЕНКА Олександра Юрійовича, ipn_0001, офіцера інформаційно-аналітичної групи штабу, у м. Тестоград, з 15 жовтня 2026 року.
+Підстава: рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1254-в (ТЕСТ-W03) від 15.10.2026); відпускний квиток № 2026/115/7 (ТЕСТ-W03) від 15.10.2026.</v>
       </c>
       <c r="D4" s="42"/>
     </row>
     <row r="5" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>318</v>
+      <c r="A5" s="42" t="str">
+        <v>W04-P01</v>
+      </c>
+      <c r="B5" s="42" t="str">
+        <v>Success</v>
+      </c>
+      <c r="C5" s="43" t="str">
+        <v>З 15 жовтня 2026 року:
+Лейтенанта БОНДАРЕНКА Олександра Юрійовича, ipn_0001, офіцера інформаційно-аналітичної групи штабу.
+Підстава: рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1255-в (ТЕСТ-W04) від 15.10.2026); відпускний квиток № 2026/115/7 (ТЕСТ-W04) від 15.10.2026.</v>
       </c>
       <c r="D5" s="42"/>
     </row>
     <row r="6" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
-        <v>296</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>319</v>
+      <c r="A6" s="42" t="str">
+        <v>W05-P01</v>
+      </c>
+      <c r="B6" s="42" t="str">
+        <v>Success</v>
+      </c>
+      <c r="C6" s="43" t="str">
+        <v>Лейтенанта БОНДАРЕНКА Олександра Юрійовича, ipn_0001, офіцера інформаційно-аналітичної групи штабу, у м. Тестоград, з 15 жовтня 2026 року.
+Підстава: рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1256-в (ТЕСТ-W05) від 15.10.2026); відпускний квиток № 2026/115/7 (ТЕСТ-W05) від 15.10.2026.</v>
       </c>
       <c r="D6" s="42"/>
     </row>
     <row r="7" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
-        <v>298</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>320</v>
+      <c r="A7" s="42" t="str">
+        <v>W06-P01</v>
+      </c>
+      <c r="B7" s="42" t="str">
+        <v>Success</v>
+      </c>
+      <c r="C7" s="43" t="str">
+        <v>З 15 жовтня 2026 року:
+Лейтенанта БОНДАРЕНКА Олександра Юрійовича, ipn_0001, офіцера інформаційно-аналітичної групи штабу.
+Підстава: рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1257-в (ТЕСТ-W06) від 15.10.2026); відпускний квиток № 2026/115/7 (ТЕСТ-W06) від 15.10.2026.</v>
       </c>
       <c r="D7" s="42"/>
     </row>
     <row r="8" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
-        <v>300</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>321</v>
+      <c r="A8" s="42" t="str">
+        <v>W07-P01</v>
+      </c>
+      <c r="B8" s="42" t="str">
+        <v>Success</v>
+      </c>
+      <c r="C8" s="43" t="str">
+        <v>Лейтенанта БОНДАРЕНКА Олександра Юрійовича, ipn_0001, офіцера інформаційно-аналітичної групи штабу, у м. Тестоград, з 15 жовтня 2026 року.
+Підстава: рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1258-в (ТЕСТ-W07) від 15.10.2026); відпускний квиток № 2026/115/7 (ТЕСТ-W07) від 15.10.2026.</v>
       </c>
       <c r="D8" s="42"/>
     </row>
     <row r="9" spans="1:4" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="42" t="s">
-        <v>302</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>322</v>
+      <c r="A9" s="42" t="str">
+        <v>W08-P01</v>
+      </c>
+      <c r="B9" s="42" t="str">
+        <v>Success</v>
+      </c>
+      <c r="C9" s="43" t="str">
+        <v>З 15 жовтня 2026 року:
+Лейтенанта БОНДАРЕНКА Олександра Юрійовича, ipn_0001, офіцера інформаційно-аналітичної групи штабу.
+Підстава: рапорт лейтенанта БОНДАРЕНКА О.Ю. (вх. № 1656/1259-в (ТЕСТ-W08) від 15.10.2026); відпускний квиток № 2026/115/7 (ТЕСТ-W08) від 15.10.2026.</v>
       </c>
       <c r="D9" s="42"/>
     </row>
     <row r="10" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
-        <v>304</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>323</v>
+      <c r="A10" s="42" t="str">
+        <v>W09-P01</v>
+      </c>
+      <c r="B10" s="42" t="str">
+        <v>Error</v>
       </c>
       <c r="C10" s="43"/>
-      <c r="D10" s="42" t="s">
-        <v>324</v>
+      <c r="D10" s="42" t="str">
+        <v>Export lookup must return exactly one row: export.Word.DepartureTreatment.lookups.1</v>
       </c>
     </row>
   </sheetData>
